--- a/public/plantilla-actos-condiciones.xlsx
+++ b/public/plantilla-actos-condiciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actos y Condiciones" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -212,8 +212,46 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -286,8 +324,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF0F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -571,6 +621,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
@@ -598,7 +659,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -670,226 +731,402 @@
     <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,6 +1136,44 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0000A651"/>
+          <bgColor rgb="0000A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C00000"/>
+          <bgColor rgb="00C00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC000"/>
+          <bgColor rgb="00FFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -1251,1029 +1526,1029 @@
   <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.77734375" customWidth="1" style="70" min="1" max="2"/>
-    <col width="13" customWidth="1" style="70" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="70" min="4" max="4"/>
-    <col width="10" customWidth="1" style="70" min="5" max="5"/>
-    <col width="15.77734375" customWidth="1" style="70" min="6" max="6"/>
-    <col width="11" customWidth="1" style="70" min="7" max="7"/>
-    <col width="15.77734375" customWidth="1" style="70" min="8" max="8"/>
-    <col width="10" customWidth="1" style="70" min="9" max="9"/>
-    <col width="15.77734375" customWidth="1" style="70" min="10" max="10"/>
-    <col width="12" customWidth="1" style="70" min="11" max="11"/>
-    <col width="13" customWidth="1" style="70" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="70" min="13" max="16384"/>
+    <col width="15.77734375" customWidth="1" style="109" min="1" max="2"/>
+    <col width="13" customWidth="1" style="109" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="109" min="4" max="4"/>
+    <col width="10" customWidth="1" style="109" min="5" max="5"/>
+    <col width="15.77734375" customWidth="1" style="109" min="6" max="6"/>
+    <col width="11" customWidth="1" style="109" min="7" max="7"/>
+    <col width="15.77734375" customWidth="1" style="109" min="8" max="8"/>
+    <col width="10" customWidth="1" style="109" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" style="109" min="10" max="10"/>
+    <col width="12" customWidth="1" style="109" min="11" max="11"/>
+    <col width="13" customWidth="1" style="109" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="109" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
-        <is>
-          <t>REPORTE DE ACTOS Y CONDICIONES INSEGURAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="56" t="n"/>
-      <c r="F3" s="56" t="n"/>
-      <c r="G3" s="56" t="n"/>
-      <c r="H3" s="56" t="n"/>
-      <c r="I3" s="56" t="n"/>
-      <c r="J3" s="56" t="n"/>
-      <c r="K3" s="56" t="n"/>
-      <c r="L3" s="56" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="J4" s="53" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="109">
+      <c r="D1" s="75" t="inlineStr">
+        <is>
+          <t>TARJETA iCAI — REPORTE DE ACTOS Y CONDICIONES INSEGURAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customHeight="1" s="109">
+      <c r="D2" s="101" t="n"/>
+      <c r="E2" s="93" t="n"/>
+      <c r="F2" s="93" t="n"/>
+      <c r="G2" s="93" t="n"/>
+      <c r="H2" s="93" t="n"/>
+      <c r="I2" s="93" t="n"/>
+      <c r="J2" s="93" t="n"/>
+      <c r="K2" s="93" t="n"/>
+      <c r="L2" s="93" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="109">
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="96" t="n"/>
+      <c r="F3" s="96" t="n"/>
+      <c r="G3" s="96" t="n"/>
+      <c r="H3" s="96" t="n"/>
+      <c r="I3" s="96" t="n"/>
+      <c r="J3" s="96" t="n"/>
+      <c r="K3" s="96" t="n"/>
+      <c r="L3" s="96" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="109">
+      <c r="J4" s="78" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="K4" s="86" t="n"/>
+      <c r="L4" s="87" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="109">
+      <c r="D5" s="105" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="I5" s="41" t="n"/>
+      <c r="I5" s="100" t="n"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="82" t="inlineStr">
         <is>
           <t>RYR-SS-011</t>
         </is>
       </c>
-      <c r="L5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="L5" s="87" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="109">
+      <c r="D6" s="106" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="I6" s="41" t="n"/>
+      <c r="I6" s="100" t="n"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="K6" s="49" t="n">
+      <c r="K6" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="109" t="n"/>
-      <c r="E7" s="109" t="n"/>
-      <c r="F7" s="109" t="n"/>
-      <c r="G7" s="109" t="n"/>
-      <c r="H7" s="109" t="n"/>
-      <c r="I7" s="81" t="n"/>
+      <c r="L6" s="87" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="109">
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="85" t="n"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="K7" s="49" t="inlineStr">
+      <c r="K7" s="82" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="110" t="n"/>
-      <c r="E8" s="110" t="n"/>
-      <c r="F8" s="110" t="n"/>
-      <c r="G8" s="110" t="n"/>
-      <c r="H8" s="110" t="n"/>
-      <c r="I8" s="81" t="n"/>
+      <c r="L7" s="87" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="109">
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="85" t="n"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="K8" s="49" t="inlineStr">
+      <c r="K8" s="82" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="L8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
-        <is>
-          <t>Todo trabajador puede y debe reportar · Reportar a tiempo evita accidentes · Decreto 1072 de 2015</t>
-        </is>
-      </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="L8" s="87" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="109">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>Tarjeta iCAI · Todo trabajador puede y debe reportar · Reportar a tiempo evita accidentes · Decreto 1072 de 2015</t>
+        </is>
+      </c>
+      <c r="B9" s="134" t="n"/>
+      <c r="C9" s="134" t="n"/>
+      <c r="D9" s="134" t="n"/>
+      <c r="E9" s="134" t="n"/>
+      <c r="F9" s="134" t="n"/>
+      <c r="G9" s="134" t="n"/>
+      <c r="H9" s="134" t="n"/>
+      <c r="I9" s="134" t="n"/>
+      <c r="J9" s="134" t="n"/>
+      <c r="K9" s="134" t="n"/>
+      <c r="L9" s="135" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="109">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>1. DATOS DEL REPORTE</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="93" t="n"/>
+      <c r="C10" s="93" t="n"/>
+      <c r="D10" s="93" t="n"/>
+      <c r="E10" s="93" t="n"/>
+      <c r="F10" s="93" t="n"/>
+      <c r="G10" s="93" t="n"/>
+      <c r="H10" s="93" t="n"/>
+      <c r="I10" s="93" t="n"/>
+      <c r="J10" s="93" t="n"/>
+      <c r="K10" s="93" t="n"/>
+      <c r="L10" s="94" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="109">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="50" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="B11" s="87" t="n"/>
+      <c r="C11" s="72" t="n"/>
+      <c r="D11" s="86" t="n"/>
+      <c r="E11" s="86" t="n"/>
+      <c r="F11" s="86" t="n"/>
+      <c r="G11" s="86" t="n"/>
+      <c r="H11" s="86" t="n"/>
+      <c r="I11" s="86" t="n"/>
+      <c r="J11" s="86" t="n"/>
+      <c r="K11" s="86" t="n"/>
+      <c r="L11" s="87" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="109">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="B12" s="87" t="n"/>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="86" t="n"/>
+      <c r="E12" s="86" t="n"/>
+      <c r="F12" s="86" t="n"/>
+      <c r="G12" s="87" t="n"/>
+      <c r="H12" s="64" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I12" s="31" t="n"/>
-      <c r="J12" s="43" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="I12" s="87" t="n"/>
+      <c r="J12" s="39" t="n"/>
+      <c r="K12" s="86" t="n"/>
+      <c r="L12" s="87" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="109">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>Fecha del hallazgo</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="B13" s="87" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="64" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="64" t="inlineStr">
         <is>
           <t>N° de reporte</t>
         </is>
       </c>
-      <c r="G13" s="48" t="n"/>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="64" t="inlineStr">
         <is>
           <t>Tipo de reporte</t>
         </is>
       </c>
-      <c r="I13" s="31" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="30" t="n"/>
-      <c r="L13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" s="70">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="I13" s="87" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="86" t="n"/>
+      <c r="L13" s="87" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="109">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>Lugar exacto del hallazgo</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-      <c r="I14" s="30" t="n"/>
-      <c r="J14" s="30" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="70">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="87" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="86" t="n"/>
+      <c r="E14" s="86" t="n"/>
+      <c r="F14" s="86" t="n"/>
+      <c r="G14" s="86" t="n"/>
+      <c r="H14" s="86" t="n"/>
+      <c r="I14" s="86" t="n"/>
+      <c r="J14" s="86" t="n"/>
+      <c r="K14" s="86" t="n"/>
+      <c r="L14" s="87" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="109">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>Quién reporta</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="B15" s="87" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="86" t="n"/>
+      <c r="F15" s="86" t="n"/>
+      <c r="G15" s="87" t="n"/>
+      <c r="H15" s="64" t="inlineStr">
         <is>
           <t>Cargo / oficio</t>
         </is>
       </c>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="30" t="n"/>
-      <c r="L15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="70">
-      <c r="A16" s="54" t="inlineStr">
+      <c r="I15" s="87" t="n"/>
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="86" t="n"/>
+      <c r="L15" s="87" t="n"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="109">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>2. CLASIFICACIÓN (marque lo que corresponda)</t>
         </is>
       </c>
-      <c r="B16" s="38" t="n"/>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
-      <c r="I16" s="38" t="n"/>
-      <c r="J16" s="38" t="n"/>
-      <c r="K16" s="38" t="n"/>
-      <c r="L16" s="47" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="70">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="B16" s="93" t="n"/>
+      <c r="C16" s="93" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="93" t="n"/>
+      <c r="H16" s="93" t="n"/>
+      <c r="I16" s="93" t="n"/>
+      <c r="J16" s="93" t="n"/>
+      <c r="K16" s="93" t="n"/>
+      <c r="L16" s="94" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="109">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>Actos inseguros (lo que hace una persona)</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
-      <c r="I17" s="30" t="n"/>
-      <c r="J17" s="30" t="n"/>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="70">
-      <c r="A18" s="89" t="inlineStr">
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="86" t="n"/>
+      <c r="H17" s="86" t="n"/>
+      <c r="I17" s="86" t="n"/>
+      <c r="J17" s="86" t="n"/>
+      <c r="K17" s="86" t="n"/>
+      <c r="L17" s="87" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="109">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>☐ No usar o usar mal los EPP</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="89" t="inlineStr">
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="87" t="n"/>
+      <c r="D18" s="61" t="inlineStr">
         <is>
           <t>☐ Omitir procedimientos o permisos</t>
         </is>
       </c>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="89" t="inlineStr">
+      <c r="E18" s="86" t="n"/>
+      <c r="F18" s="87" t="n"/>
+      <c r="G18" s="61" t="inlineStr">
         <is>
           <t>☐ Trabajar sin ATS o sin autorización</t>
         </is>
       </c>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="31" t="n"/>
-      <c r="J18" s="89" t="inlineStr">
+      <c r="H18" s="86" t="n"/>
+      <c r="I18" s="87" t="n"/>
+      <c r="J18" s="61" t="inlineStr">
         <is>
           <t>☐ Usar herramientas o equipos inadecuados</t>
         </is>
       </c>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="70">
-      <c r="A19" s="89" t="inlineStr">
+      <c r="K18" s="86" t="n"/>
+      <c r="L18" s="87" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="109">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>☐ Trabajar en alturas sin protección</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="89" t="inlineStr">
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="87" t="n"/>
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>☐ Bloquear salidas o rutas de evacuación</t>
         </is>
       </c>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="89" t="inlineStr">
+      <c r="E19" s="86" t="n"/>
+      <c r="F19" s="87" t="n"/>
+      <c r="G19" s="61" t="inlineStr">
         <is>
           <t>☐ Cargas o posturas inadecuadas</t>
         </is>
       </c>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="89" t="inlineStr">
+      <c r="H19" s="86" t="n"/>
+      <c r="I19" s="87" t="n"/>
+      <c r="J19" s="61" t="inlineStr">
         <is>
           <t>☐ Distracción o uso del celular</t>
         </is>
       </c>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="70">
-      <c r="A20" s="89" t="inlineStr">
+      <c r="K19" s="86" t="n"/>
+      <c r="L19" s="87" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="109">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>☐ Bromas o juegos en el área de trabajo</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="89" t="inlineStr">
+      <c r="B20" s="86" t="n"/>
+      <c r="C20" s="87" t="n"/>
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>☐ Trabajar bajo alcohol o sustancias</t>
         </is>
       </c>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="89" t="inlineStr">
+      <c r="E20" s="86" t="n"/>
+      <c r="F20" s="87" t="n"/>
+      <c r="G20" s="61" t="inlineStr">
         <is>
           <t>☐ Manejo inseguro de vehículos</t>
         </is>
       </c>
-      <c r="H20" s="30" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="89" t="inlineStr">
+      <c r="H20" s="86" t="n"/>
+      <c r="I20" s="87" t="n"/>
+      <c r="J20" s="61" t="inlineStr">
         <is>
           <t>☐ Otro acto: ____________</t>
         </is>
       </c>
-      <c r="K20" s="30" t="n"/>
-      <c r="L20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="70">
-      <c r="A21" s="88" t="inlineStr">
+      <c r="K20" s="86" t="n"/>
+      <c r="L20" s="87" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="109">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>Condiciones inseguras (lo que hay en el entorno)</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
-      <c r="I21" s="30" t="n"/>
-      <c r="J21" s="30" t="n"/>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" s="70">
-      <c r="A22" s="89" t="inlineStr">
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="86" t="n"/>
+      <c r="D21" s="86" t="n"/>
+      <c r="E21" s="86" t="n"/>
+      <c r="F21" s="86" t="n"/>
+      <c r="G21" s="86" t="n"/>
+      <c r="H21" s="86" t="n"/>
+      <c r="I21" s="86" t="n"/>
+      <c r="J21" s="86" t="n"/>
+      <c r="K21" s="86" t="n"/>
+      <c r="L21" s="87" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" s="109">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>☐ Desorden o falta de aseo</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="89" t="inlineStr">
+      <c r="B22" s="86" t="n"/>
+      <c r="C22" s="87" t="n"/>
+      <c r="D22" s="61" t="inlineStr">
         <is>
           <t>☐ Herramienta o equipo defectuoso</t>
         </is>
       </c>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="89" t="inlineStr">
+      <c r="E22" s="86" t="n"/>
+      <c r="F22" s="87" t="n"/>
+      <c r="G22" s="61" t="inlineStr">
         <is>
           <t>☐ Falta de señalización o demarcación</t>
         </is>
       </c>
-      <c r="H22" s="30" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="89" t="inlineStr">
+      <c r="H22" s="86" t="n"/>
+      <c r="I22" s="87" t="n"/>
+      <c r="J22" s="61" t="inlineStr">
         <is>
           <t>☐ Falta de guardas o protecciones</t>
         </is>
       </c>
-      <c r="K22" s="30" t="n"/>
-      <c r="L22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" s="70">
-      <c r="A23" s="89" t="inlineStr">
+      <c r="K22" s="86" t="n"/>
+      <c r="L22" s="87" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" s="109">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>☐ Instalación eléctrica deficiente</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="89" t="inlineStr">
+      <c r="B23" s="86" t="n"/>
+      <c r="C23" s="87" t="n"/>
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>☐ Andamio, escalera o plataforma en mal estado</t>
         </is>
       </c>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="89" t="inlineStr">
+      <c r="E23" s="86" t="n"/>
+      <c r="F23" s="87" t="n"/>
+      <c r="G23" s="61" t="inlineStr">
         <is>
           <t>☐ Iluminación o ventilación insuficiente</t>
         </is>
       </c>
-      <c r="H23" s="30" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="89" t="inlineStr">
+      <c r="H23" s="86" t="n"/>
+      <c r="I23" s="87" t="n"/>
+      <c r="J23" s="61" t="inlineStr">
         <is>
           <t>☐ Piso irregular, húmedo o con huecos</t>
         </is>
       </c>
-      <c r="K23" s="30" t="n"/>
-      <c r="L23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" s="70">
-      <c r="A24" s="89" t="inlineStr">
+      <c r="K23" s="86" t="n"/>
+      <c r="L23" s="87" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="109">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>☐ Material mal almacenado</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="89" t="inlineStr">
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="61" t="inlineStr">
         <is>
           <t>☐ Fugas o derrames</t>
         </is>
       </c>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="89" t="inlineStr">
+      <c r="E24" s="86" t="n"/>
+      <c r="F24" s="87" t="n"/>
+      <c r="G24" s="61" t="inlineStr">
         <is>
           <t>☐ Falta de extintor o de botiquín</t>
         </is>
       </c>
-      <c r="H24" s="30" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="89" t="inlineStr">
+      <c r="H24" s="86" t="n"/>
+      <c r="I24" s="87" t="n"/>
+      <c r="J24" s="61" t="inlineStr">
         <is>
           <t>☐ Otra condición: ____________</t>
         </is>
       </c>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="70">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="K24" s="86" t="n"/>
+      <c r="L24" s="87" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="109">
+      <c r="A25" s="71" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN DEL HALLAZGO</t>
         </is>
       </c>
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-      <c r="E25" s="38" t="n"/>
-      <c r="F25" s="38" t="n"/>
-      <c r="G25" s="38" t="n"/>
-      <c r="H25" s="38" t="n"/>
-      <c r="I25" s="38" t="n"/>
-      <c r="J25" s="38" t="n"/>
-      <c r="K25" s="38" t="n"/>
-      <c r="L25" s="47" t="n"/>
-    </row>
-    <row r="26" ht="48" customHeight="1" s="70">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="B25" s="93" t="n"/>
+      <c r="C25" s="93" t="n"/>
+      <c r="D25" s="93" t="n"/>
+      <c r="E25" s="93" t="n"/>
+      <c r="F25" s="93" t="n"/>
+      <c r="G25" s="93" t="n"/>
+      <c r="H25" s="93" t="n"/>
+      <c r="I25" s="93" t="n"/>
+      <c r="J25" s="93" t="n"/>
+      <c r="K25" s="93" t="n"/>
+      <c r="L25" s="94" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="109">
+      <c r="A26" s="64" t="inlineStr">
         <is>
           <t>¿Qué se observó?</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-      <c r="I26" s="30" t="n"/>
-      <c r="J26" s="30" t="n"/>
-      <c r="K26" s="30" t="n"/>
-      <c r="L26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="34.05" customHeight="1" s="70">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="B26" s="87" t="n"/>
+      <c r="C26" s="95" t="n"/>
+      <c r="D26" s="86" t="n"/>
+      <c r="E26" s="86" t="n"/>
+      <c r="F26" s="86" t="n"/>
+      <c r="G26" s="86" t="n"/>
+      <c r="H26" s="86" t="n"/>
+      <c r="I26" s="86" t="n"/>
+      <c r="J26" s="86" t="n"/>
+      <c r="K26" s="86" t="n"/>
+      <c r="L26" s="87" t="n"/>
+    </row>
+    <row r="27" ht="34.05" customHeight="1" s="109">
+      <c r="A27" s="64" t="inlineStr">
         <is>
           <t>Posible consecuencia</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n"/>
-      <c r="J27" s="30" t="n"/>
-      <c r="K27" s="30" t="n"/>
-      <c r="L27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="21" customHeight="1" s="70">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="B27" s="87" t="n"/>
+      <c r="C27" s="95" t="n"/>
+      <c r="D27" s="86" t="n"/>
+      <c r="E27" s="86" t="n"/>
+      <c r="F27" s="86" t="n"/>
+      <c r="G27" s="86" t="n"/>
+      <c r="H27" s="86" t="n"/>
+      <c r="I27" s="86" t="n"/>
+      <c r="J27" s="86" t="n"/>
+      <c r="K27" s="86" t="n"/>
+      <c r="L27" s="87" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1" s="109">
+      <c r="A28" s="64" t="inlineStr">
         <is>
           <t>Persona(s) involucrada(s) (opcional)</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="30" t="n"/>
-      <c r="I28" s="30" t="n"/>
-      <c r="J28" s="30" t="n"/>
-      <c r="K28" s="30" t="n"/>
-      <c r="L28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="21" customHeight="1" s="70">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="B28" s="87" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="86" t="n"/>
+      <c r="E28" s="86" t="n"/>
+      <c r="F28" s="86" t="n"/>
+      <c r="G28" s="86" t="n"/>
+      <c r="H28" s="86" t="n"/>
+      <c r="I28" s="86" t="n"/>
+      <c r="J28" s="86" t="n"/>
+      <c r="K28" s="86" t="n"/>
+      <c r="L28" s="87" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1" s="109">
+      <c r="A29" s="64" t="inlineStr">
         <is>
           <t>Probabilidad</t>
         </is>
       </c>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="48" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="B29" s="87" t="n"/>
+      <c r="C29" s="59" t="n"/>
+      <c r="D29" s="87" t="n"/>
+      <c r="E29" s="64" t="inlineStr">
         <is>
           <t>Severidad</t>
         </is>
       </c>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="48" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="33" t="inlineStr">
+      <c r="F29" s="87" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="64" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="48" t="n"/>
-      <c r="L29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="70">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="J29" s="87" t="n"/>
+      <c r="K29" s="59" t="n"/>
+      <c r="L29" s="87" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="109">
+      <c r="A30" s="71" t="inlineStr">
         <is>
           <t>4. ACCIÓN INMEDIATA Y RECOMENDACIÓN</t>
         </is>
       </c>
-      <c r="B30" s="38" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="38" t="n"/>
-      <c r="E30" s="38" t="n"/>
-      <c r="F30" s="38" t="n"/>
-      <c r="G30" s="38" t="n"/>
-      <c r="H30" s="38" t="n"/>
-      <c r="I30" s="38" t="n"/>
-      <c r="J30" s="38" t="n"/>
-      <c r="K30" s="38" t="n"/>
-      <c r="L30" s="47" t="n"/>
-    </row>
-    <row r="31" ht="34.05" customHeight="1" s="70">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="B30" s="93" t="n"/>
+      <c r="C30" s="93" t="n"/>
+      <c r="D30" s="93" t="n"/>
+      <c r="E30" s="93" t="n"/>
+      <c r="F30" s="93" t="n"/>
+      <c r="G30" s="93" t="n"/>
+      <c r="H30" s="93" t="n"/>
+      <c r="I30" s="93" t="n"/>
+      <c r="J30" s="93" t="n"/>
+      <c r="K30" s="93" t="n"/>
+      <c r="L30" s="94" t="n"/>
+    </row>
+    <row r="31" ht="34.05" customHeight="1" s="109">
+      <c r="A31" s="64" t="inlineStr">
         <is>
           <t>Acción inmediata tomada</t>
         </is>
       </c>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n"/>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="34.05" customHeight="1" s="70">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="B31" s="87" t="n"/>
+      <c r="C31" s="95" t="n"/>
+      <c r="D31" s="86" t="n"/>
+      <c r="E31" s="86" t="n"/>
+      <c r="F31" s="86" t="n"/>
+      <c r="G31" s="86" t="n"/>
+      <c r="H31" s="86" t="n"/>
+      <c r="I31" s="86" t="n"/>
+      <c r="J31" s="86" t="n"/>
+      <c r="K31" s="86" t="n"/>
+      <c r="L31" s="87" t="n"/>
+    </row>
+    <row r="32" ht="34.05" customHeight="1" s="109">
+      <c r="A32" s="64" t="inlineStr">
         <is>
           <t>Recomendación o acción correctiva propuesta</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="30" t="n"/>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="30" t="n"/>
-      <c r="K32" s="30" t="n"/>
-      <c r="L32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1" s="70">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="B32" s="87" t="n"/>
+      <c r="C32" s="95" t="n"/>
+      <c r="D32" s="86" t="n"/>
+      <c r="E32" s="86" t="n"/>
+      <c r="F32" s="86" t="n"/>
+      <c r="G32" s="86" t="n"/>
+      <c r="H32" s="86" t="n"/>
+      <c r="I32" s="86" t="n"/>
+      <c r="J32" s="86" t="n"/>
+      <c r="K32" s="86" t="n"/>
+      <c r="L32" s="87" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1" s="109">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>Responsable de la corrección</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="33" t="inlineStr">
+      <c r="B33" s="87" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="86" t="n"/>
+      <c r="E33" s="86" t="n"/>
+      <c r="F33" s="86" t="n"/>
+      <c r="G33" s="87" t="n"/>
+      <c r="H33" s="64" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
       </c>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="48" t="n"/>
-      <c r="K33" s="30" t="n"/>
-      <c r="L33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="70">
-      <c r="A34" s="54" t="inlineStr">
+      <c r="I33" s="87" t="n"/>
+      <c r="J33" s="59" t="n"/>
+      <c r="K33" s="86" t="n"/>
+      <c r="L33" s="87" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="109">
+      <c r="A34" s="71" t="inlineStr">
         <is>
           <t>5. EVIDENCIA FOTOGRÁFICA</t>
         </is>
       </c>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="38" t="n"/>
-      <c r="K34" s="38" t="n"/>
-      <c r="L34" s="47" t="n"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="70">
+      <c r="B34" s="93" t="n"/>
+      <c r="C34" s="93" t="n"/>
+      <c r="D34" s="93" t="n"/>
+      <c r="E34" s="93" t="n"/>
+      <c r="F34" s="93" t="n"/>
+      <c r="G34" s="93" t="n"/>
+      <c r="H34" s="93" t="n"/>
+      <c r="I34" s="93" t="n"/>
+      <c r="J34" s="93" t="n"/>
+      <c r="K34" s="93" t="n"/>
+      <c r="L34" s="94" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="109">
       <c r="A35" s="111" t="n"/>
-      <c r="B35" s="56" t="n"/>
-      <c r="C35" s="56" t="n"/>
-      <c r="D35" s="56" t="n"/>
-      <c r="E35" s="56" t="n"/>
-      <c r="F35" s="45" t="n"/>
+      <c r="B35" s="96" t="n"/>
+      <c r="C35" s="96" t="n"/>
+      <c r="D35" s="96" t="n"/>
+      <c r="E35" s="96" t="n"/>
+      <c r="F35" s="97" t="n"/>
       <c r="G35" s="111" t="n"/>
-      <c r="H35" s="56" t="n"/>
-      <c r="I35" s="56" t="n"/>
-      <c r="J35" s="56" t="n"/>
-      <c r="K35" s="56" t="n"/>
-      <c r="L35" s="45" t="n"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="70">
-      <c r="A36" s="46" t="n"/>
-      <c r="F36" s="41" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="L36" s="41" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="70">
-      <c r="A37" s="46" t="n"/>
-      <c r="F37" s="41" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="L37" s="41" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="70">
-      <c r="A38" s="46" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="46" t="n"/>
-      <c r="L38" s="41" t="n"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="70">
-      <c r="A39" s="46" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="46" t="n"/>
-      <c r="L39" s="41" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="70">
-      <c r="A40" s="46" t="n"/>
-      <c r="F40" s="41" t="n"/>
-      <c r="G40" s="46" t="n"/>
-      <c r="L40" s="41" t="n"/>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" s="70">
-      <c r="A41" s="46" t="n"/>
-      <c r="F41" s="41" t="n"/>
-      <c r="G41" s="46" t="n"/>
-      <c r="L41" s="41" t="n"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="70">
-      <c r="A42" s="46" t="n"/>
-      <c r="F42" s="41" t="n"/>
-      <c r="G42" s="46" t="n"/>
-      <c r="L42" s="41" t="n"/>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" s="70">
-      <c r="A43" s="46" t="n"/>
-      <c r="F43" s="41" t="n"/>
-      <c r="G43" s="46" t="n"/>
-      <c r="L43" s="41" t="n"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1" s="70">
-      <c r="A44" s="46" t="n"/>
-      <c r="F44" s="41" t="n"/>
-      <c r="G44" s="46" t="n"/>
-      <c r="L44" s="41" t="n"/>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="70">
-      <c r="A45" s="46" t="n"/>
-      <c r="F45" s="41" t="n"/>
-      <c r="G45" s="46" t="n"/>
-      <c r="L45" s="41" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="70">
-      <c r="A46" s="46" t="n"/>
-      <c r="F46" s="41" t="n"/>
-      <c r="G46" s="46" t="n"/>
-      <c r="L46" s="41" t="n"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="70">
-      <c r="A47" s="46" t="n"/>
-      <c r="F47" s="41" t="n"/>
-      <c r="G47" s="46" t="n"/>
-      <c r="L47" s="41" t="n"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="70">
-      <c r="A48" s="46" t="n"/>
-      <c r="F48" s="41" t="n"/>
-      <c r="G48" s="46" t="n"/>
-      <c r="L48" s="41" t="n"/>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="70">
-      <c r="A49" s="46" t="n"/>
-      <c r="F49" s="41" t="n"/>
-      <c r="G49" s="46" t="n"/>
-      <c r="L49" s="41" t="n"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="70">
-      <c r="A50" s="37" t="n"/>
-      <c r="B50" s="38" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="38" t="n"/>
-      <c r="E50" s="38" t="n"/>
-      <c r="F50" s="47" t="n"/>
-      <c r="G50" s="37" t="n"/>
-      <c r="H50" s="38" t="n"/>
-      <c r="I50" s="38" t="n"/>
-      <c r="J50" s="38" t="n"/>
-      <c r="K50" s="38" t="n"/>
-      <c r="L50" s="47" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="70">
+      <c r="H35" s="96" t="n"/>
+      <c r="I35" s="96" t="n"/>
+      <c r="J35" s="96" t="n"/>
+      <c r="K35" s="96" t="n"/>
+      <c r="L35" s="97" t="n"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="109">
+      <c r="A36" s="98" t="n"/>
+      <c r="F36" s="100" t="n"/>
+      <c r="G36" s="98" t="n"/>
+      <c r="L36" s="100" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="109">
+      <c r="A37" s="98" t="n"/>
+      <c r="F37" s="100" t="n"/>
+      <c r="G37" s="98" t="n"/>
+      <c r="L37" s="100" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="109">
+      <c r="A38" s="98" t="n"/>
+      <c r="F38" s="100" t="n"/>
+      <c r="G38" s="98" t="n"/>
+      <c r="L38" s="100" t="n"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="109">
+      <c r="A39" s="98" t="n"/>
+      <c r="F39" s="100" t="n"/>
+      <c r="G39" s="98" t="n"/>
+      <c r="L39" s="100" t="n"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="109">
+      <c r="A40" s="98" t="n"/>
+      <c r="F40" s="100" t="n"/>
+      <c r="G40" s="98" t="n"/>
+      <c r="L40" s="100" t="n"/>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="109">
+      <c r="A41" s="98" t="n"/>
+      <c r="F41" s="100" t="n"/>
+      <c r="G41" s="98" t="n"/>
+      <c r="L41" s="100" t="n"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="109">
+      <c r="A42" s="98" t="n"/>
+      <c r="F42" s="100" t="n"/>
+      <c r="G42" s="98" t="n"/>
+      <c r="L42" s="100" t="n"/>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="109">
+      <c r="A43" s="98" t="n"/>
+      <c r="F43" s="100" t="n"/>
+      <c r="G43" s="98" t="n"/>
+      <c r="L43" s="100" t="n"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="109">
+      <c r="A44" s="98" t="n"/>
+      <c r="F44" s="100" t="n"/>
+      <c r="G44" s="98" t="n"/>
+      <c r="L44" s="100" t="n"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="109">
+      <c r="A45" s="98" t="n"/>
+      <c r="F45" s="100" t="n"/>
+      <c r="G45" s="98" t="n"/>
+      <c r="L45" s="100" t="n"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="109">
+      <c r="A46" s="98" t="n"/>
+      <c r="F46" s="100" t="n"/>
+      <c r="G46" s="98" t="n"/>
+      <c r="L46" s="100" t="n"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="109">
+      <c r="A47" s="98" t="n"/>
+      <c r="F47" s="100" t="n"/>
+      <c r="G47" s="98" t="n"/>
+      <c r="L47" s="100" t="n"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="109">
+      <c r="A48" s="98" t="n"/>
+      <c r="F48" s="100" t="n"/>
+      <c r="G48" s="98" t="n"/>
+      <c r="L48" s="100" t="n"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="109">
+      <c r="A49" s="98" t="n"/>
+      <c r="F49" s="100" t="n"/>
+      <c r="G49" s="98" t="n"/>
+      <c r="L49" s="100" t="n"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" s="109">
+      <c r="A50" s="101" t="n"/>
+      <c r="B50" s="93" t="n"/>
+      <c r="C50" s="93" t="n"/>
+      <c r="D50" s="93" t="n"/>
+      <c r="E50" s="93" t="n"/>
+      <c r="F50" s="94" t="n"/>
+      <c r="G50" s="101" t="n"/>
+      <c r="H50" s="93" t="n"/>
+      <c r="I50" s="93" t="n"/>
+      <c r="J50" s="93" t="n"/>
+      <c r="K50" s="93" t="n"/>
+      <c r="L50" s="94" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="109">
       <c r="A51" s="112" t="inlineStr">
         <is>
           <t>ANTES — el acto o la condición observada</t>
         </is>
       </c>
-      <c r="B51" s="30" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="30" t="n"/>
-      <c r="E51" s="30" t="n"/>
-      <c r="F51" s="31" t="n"/>
+      <c r="B51" s="86" t="n"/>
+      <c r="C51" s="86" t="n"/>
+      <c r="D51" s="86" t="n"/>
+      <c r="E51" s="86" t="n"/>
+      <c r="F51" s="87" t="n"/>
       <c r="G51" s="112" t="inlineStr">
         <is>
           <t>DESPUÉS — ya corregido (cuando aplique)</t>
         </is>
       </c>
-      <c r="H51" s="30" t="n"/>
-      <c r="I51" s="30" t="n"/>
-      <c r="J51" s="30" t="n"/>
-      <c r="K51" s="30" t="n"/>
-      <c r="L51" s="31" t="n"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" s="70">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="H51" s="86" t="n"/>
+      <c r="I51" s="86" t="n"/>
+      <c r="J51" s="86" t="n"/>
+      <c r="K51" s="86" t="n"/>
+      <c r="L51" s="87" t="n"/>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" s="109">
+      <c r="A52" s="71" t="inlineStr">
         <is>
           <t>6. SEGUIMIENTO Y CIERRE</t>
         </is>
       </c>
-      <c r="B52" s="38" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="38" t="n"/>
-      <c r="E52" s="38" t="n"/>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="38" t="n"/>
-      <c r="H52" s="38" t="n"/>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="38" t="n"/>
-      <c r="K52" s="38" t="n"/>
-      <c r="L52" s="47" t="n"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" s="70">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="B52" s="93" t="n"/>
+      <c r="C52" s="93" t="n"/>
+      <c r="D52" s="93" t="n"/>
+      <c r="E52" s="93" t="n"/>
+      <c r="F52" s="93" t="n"/>
+      <c r="G52" s="93" t="n"/>
+      <c r="H52" s="93" t="n"/>
+      <c r="I52" s="93" t="n"/>
+      <c r="J52" s="93" t="n"/>
+      <c r="K52" s="93" t="n"/>
+      <c r="L52" s="94" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" s="109">
+      <c r="A53" s="64" t="inlineStr">
         <is>
           <t>¿Quedó corregido?</t>
         </is>
       </c>
-      <c r="B53" s="31" t="n"/>
-      <c r="C53" s="48" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="33" t="inlineStr">
+      <c r="B53" s="87" t="n"/>
+      <c r="C53" s="59" t="n"/>
+      <c r="D53" s="87" t="n"/>
+      <c r="E53" s="64" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
-      <c r="F53" s="31" t="n"/>
-      <c r="G53" s="48" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="33" t="inlineStr">
+      <c r="F53" s="87" t="n"/>
+      <c r="G53" s="59" t="n"/>
+      <c r="H53" s="87" t="n"/>
+      <c r="I53" s="64" t="inlineStr">
         <is>
           <t>Verificó el cierre</t>
         </is>
       </c>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="43" t="n"/>
-      <c r="L53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="30" customHeight="1" s="70">
-      <c r="A54" s="33" t="inlineStr">
+      <c r="J53" s="87" t="n"/>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="87" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" s="109">
+      <c r="A54" s="64" t="inlineStr">
         <is>
           <t>Observaciones del cierre</t>
         </is>
       </c>
-      <c r="B54" s="31" t="n"/>
-      <c r="C54" s="52" t="n"/>
-      <c r="D54" s="30" t="n"/>
-      <c r="E54" s="30" t="n"/>
-      <c r="F54" s="30" t="n"/>
-      <c r="G54" s="30" t="n"/>
-      <c r="H54" s="30" t="n"/>
-      <c r="I54" s="30" t="n"/>
-      <c r="J54" s="30" t="n"/>
-      <c r="K54" s="30" t="n"/>
-      <c r="L54" s="31" t="n"/>
-    </row>
-    <row r="55" ht="16.5" customHeight="1" s="70">
-      <c r="A55" s="54" t="inlineStr">
+      <c r="B54" s="87" t="n"/>
+      <c r="C54" s="95" t="n"/>
+      <c r="D54" s="86" t="n"/>
+      <c r="E54" s="86" t="n"/>
+      <c r="F54" s="86" t="n"/>
+      <c r="G54" s="86" t="n"/>
+      <c r="H54" s="86" t="n"/>
+      <c r="I54" s="86" t="n"/>
+      <c r="J54" s="86" t="n"/>
+      <c r="K54" s="86" t="n"/>
+      <c r="L54" s="87" t="n"/>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" s="109">
+      <c r="A55" s="71" t="inlineStr">
         <is>
           <t>7. FIRMAS</t>
         </is>
       </c>
-      <c r="B55" s="38" t="n"/>
-      <c r="C55" s="38" t="n"/>
-      <c r="D55" s="38" t="n"/>
-      <c r="E55" s="38" t="n"/>
-      <c r="F55" s="38" t="n"/>
-      <c r="G55" s="38" t="n"/>
-      <c r="H55" s="38" t="n"/>
-      <c r="I55" s="38" t="n"/>
-      <c r="J55" s="38" t="n"/>
-      <c r="K55" s="38" t="n"/>
-      <c r="L55" s="47" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1" s="70">
-      <c r="A56" s="51" t="inlineStr">
+      <c r="B55" s="93" t="n"/>
+      <c r="C55" s="93" t="n"/>
+      <c r="D55" s="93" t="n"/>
+      <c r="E55" s="93" t="n"/>
+      <c r="F55" s="93" t="n"/>
+      <c r="G55" s="93" t="n"/>
+      <c r="H55" s="93" t="n"/>
+      <c r="I55" s="93" t="n"/>
+      <c r="J55" s="93" t="n"/>
+      <c r="K55" s="93" t="n"/>
+      <c r="L55" s="94" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="109">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>QUIEN REPORTA</t>
         </is>
       </c>
-      <c r="B56" s="30" t="n"/>
-      <c r="C56" s="30" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="51" t="inlineStr">
+      <c r="B56" s="86" t="n"/>
+      <c r="C56" s="86" t="n"/>
+      <c r="D56" s="87" t="n"/>
+      <c r="E56" s="42" t="inlineStr">
         <is>
           <t>RECIBE — RESPONSABLE SST / RESIDENTE</t>
         </is>
       </c>
-      <c r="F56" s="30" t="n"/>
-      <c r="G56" s="30" t="n"/>
-      <c r="H56" s="31" t="n"/>
-      <c r="I56" s="51" t="inlineStr">
+      <c r="F56" s="86" t="n"/>
+      <c r="G56" s="86" t="n"/>
+      <c r="H56" s="87" t="n"/>
+      <c r="I56" s="42" t="inlineStr">
         <is>
           <t>VERIFICA EL CIERRE</t>
         </is>
       </c>
-      <c r="J56" s="30" t="n"/>
-      <c r="K56" s="30" t="n"/>
-      <c r="L56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="42" customHeight="1" s="70">
-      <c r="A57" s="39" t="inlineStr">
+      <c r="J56" s="86" t="n"/>
+      <c r="K56" s="86" t="n"/>
+      <c r="L56" s="87" t="n"/>
+    </row>
+    <row r="57" ht="42" customHeight="1" s="109">
+      <c r="A57" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B57" s="31" t="n"/>
-      <c r="C57" s="43" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="39" t="inlineStr">
+      <c r="B57" s="87" t="n"/>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="87" t="n"/>
+      <c r="E57" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F57" s="31" t="n"/>
-      <c r="G57" s="43" t="n"/>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="39" t="inlineStr">
+      <c r="F57" s="87" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="87" t="n"/>
+      <c r="I57" s="38" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="43" t="n"/>
-      <c r="L57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" s="70">
-      <c r="A58" s="39" t="inlineStr">
+      <c r="J57" s="87" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="87" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" s="109">
+      <c r="A58" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B58" s="31" t="n"/>
-      <c r="C58" s="43" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="39" t="inlineStr">
+      <c r="B58" s="87" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="87" t="n"/>
+      <c r="E58" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="43" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="39" t="inlineStr">
+      <c r="F58" s="87" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="87" t="n"/>
+      <c r="I58" s="38" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="43" t="n"/>
-      <c r="L58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="21" customHeight="1" s="70">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="J58" s="87" t="n"/>
+      <c r="K58" s="39" t="n"/>
+      <c r="L58" s="87" t="n"/>
+    </row>
+    <row r="59" ht="21" customHeight="1" s="109">
+      <c r="A59" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B59" s="31" t="n"/>
-      <c r="C59" s="43" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="39" t="inlineStr">
+      <c r="B59" s="87" t="n"/>
+      <c r="C59" s="39" t="n"/>
+      <c r="D59" s="87" t="n"/>
+      <c r="E59" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="F59" s="31" t="n"/>
-      <c r="G59" s="43" t="n"/>
-      <c r="H59" s="31" t="n"/>
-      <c r="I59" s="39" t="inlineStr">
+      <c r="F59" s="87" t="n"/>
+      <c r="G59" s="39" t="n"/>
+      <c r="H59" s="87" t="n"/>
+      <c r="I59" s="38" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="43" t="n"/>
-      <c r="L59" s="31" t="n"/>
+      <c r="J59" s="87" t="n"/>
+      <c r="K59" s="39" t="n"/>
+      <c r="L59" s="87" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="61" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G60" s="63">
+      <c r="G60" s="88">
         <f>K5</f>
         <v/>
       </c>
@@ -2292,15 +2567,15 @@
     <mergeCell ref="K58:L58"/>
     <mergeCell ref="A52:L52"/>
     <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D5:I5"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D5:I5"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="A34:L34"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="K53:L53"/>
     <mergeCell ref="A56:D56"/>
-    <mergeCell ref="K53:L53"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="A28:B28"/>
@@ -2346,18 +2621,18 @@
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="C14:L14"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A12:B12"/>
     <mergeCell ref="E59:F59"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="G22:I22"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="K8:L8"/>
     <mergeCell ref="G60:L60"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="C54:L54"/>
-    <mergeCell ref="D20:F20"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="A35:F50"/>
@@ -2374,8 +2649,8 @@
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="I53:J53"/>
+    <mergeCell ref="J12:L12"/>
     <mergeCell ref="G51:L51"/>
-    <mergeCell ref="J12:L12"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="A19:C19"/>
@@ -2384,8 +2659,8 @@
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="A30:L30"/>
+    <mergeCell ref="D19:F19"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="D19:F19"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="H33:I33"/>

--- a/public/plantilla-actos-condiciones.xlsx
+++ b/public/plantilla-actos-condiciones.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actos y Condiciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCAI" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="32">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,14 +75,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
@@ -165,14 +157,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="9.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,13 +204,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
@@ -250,19 +227,83 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1B2A45"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -274,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -308,20 +337,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FFEEF1F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -332,12 +349,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF0F6"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -467,19 +544,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -573,26 +637,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -620,13 +664,183 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
-        <color rgb="FF9AA3B2"/>
+        <color rgb="FF0B1F33"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
       <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,9 +848,92 @@
       <left/>
       <right/>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -645,7 +942,75 @@
         <color theme="3" tint="0.5999633777886288"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -659,381 +1024,296 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1042,90 +1322,612 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1136,45 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="0000A651"/>
-          <bgColor rgb="0000A651"/>
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C00000"/>
-          <bgColor rgb="00C00000"/>
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00000000"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC000"/>
-          <bgColor rgb="00FFC000"/>
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -1526,1029 +2437,1006 @@
   <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.77734375" customWidth="1" style="109" min="1" max="2"/>
-    <col width="13" customWidth="1" style="109" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="109" min="4" max="4"/>
-    <col width="10" customWidth="1" style="109" min="5" max="5"/>
-    <col width="15.77734375" customWidth="1" style="109" min="6" max="6"/>
-    <col width="11" customWidth="1" style="109" min="7" max="7"/>
-    <col width="15.77734375" customWidth="1" style="109" min="8" max="8"/>
-    <col width="10" customWidth="1" style="109" min="9" max="9"/>
-    <col width="15.77734375" customWidth="1" style="109" min="10" max="10"/>
-    <col width="12" customWidth="1" style="109" min="11" max="11"/>
-    <col width="13" customWidth="1" style="109" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="109" min="13" max="16384"/>
+    <col width="15.77734375" customWidth="1" style="127" min="1" max="2"/>
+    <col width="13" customWidth="1" style="127" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="127" min="4" max="8"/>
+    <col width="10" customWidth="1" style="127" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" style="127" min="10" max="10"/>
+    <col width="12" customWidth="1" style="127" min="11" max="11"/>
+    <col width="13" customWidth="1" style="127" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="127" min="13" max="13"/>
+    <col width="8.88671875" customWidth="1" style="127" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="109">
-      <c r="D1" s="75" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="D1" s="133" t="inlineStr">
         <is>
           <t>TARJETA iCAI — REPORTE DE ACTOS Y CONDICIONES INSEGURAS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="109">
-      <c r="D2" s="101" t="n"/>
-      <c r="E2" s="93" t="n"/>
-      <c r="F2" s="93" t="n"/>
-      <c r="G2" s="93" t="n"/>
-      <c r="H2" s="93" t="n"/>
-      <c r="I2" s="93" t="n"/>
-      <c r="J2" s="93" t="n"/>
-      <c r="K2" s="93" t="n"/>
-      <c r="L2" s="93" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="109">
-      <c r="D3" s="77" t="n"/>
-      <c r="E3" s="96" t="n"/>
-      <c r="F3" s="96" t="n"/>
-      <c r="G3" s="96" t="n"/>
-      <c r="H3" s="96" t="n"/>
-      <c r="I3" s="96" t="n"/>
-      <c r="J3" s="96" t="n"/>
-      <c r="K3" s="96" t="n"/>
-      <c r="L3" s="96" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="109">
-      <c r="J4" s="78" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127">
+      <c r="D2" s="96" t="n"/>
+      <c r="E2" s="98" t="n"/>
+      <c r="F2" s="98" t="n"/>
+      <c r="G2" s="98" t="n"/>
+      <c r="H2" s="98" t="n"/>
+      <c r="I2" s="98" t="n"/>
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="n"/>
+      <c r="L2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="D3" s="60" t="n"/>
+      <c r="E3" s="104" t="n"/>
+      <c r="F3" s="104" t="n"/>
+      <c r="G3" s="104" t="n"/>
+      <c r="H3" s="104" t="n"/>
+      <c r="I3" s="104" t="n"/>
+      <c r="J3" s="104" t="n"/>
+      <c r="K3" s="104" t="n"/>
+      <c r="L3" s="104" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="J4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="K4" s="86" t="n"/>
-      <c r="L4" s="87" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="109">
-      <c r="D5" s="105" t="inlineStr">
+      <c r="K4" s="93" t="n"/>
+      <c r="L4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="I5" s="100" t="n"/>
+      <c r="I5" s="92" t="n"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="K5" s="82" t="inlineStr">
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-011</t>
         </is>
       </c>
-      <c r="L5" s="87" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="109">
-      <c r="D6" s="106" t="inlineStr">
+      <c r="L5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="D6" s="90" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="I6" s="100" t="n"/>
+      <c r="I6" s="92" t="n"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="K6" s="82" t="n">
+      <c r="K6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="87" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="109">
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="85" t="n"/>
+      <c r="L6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="67" t="n"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="K7" s="82" t="inlineStr">
+      <c r="K7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="L7" s="87" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="109">
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="85" t="n"/>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="L7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="67" t="n"/>
+      <c r="J8" s="254" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="K8" s="82" t="inlineStr">
+      <c r="K8" s="58" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="L8" s="87" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="109">
-      <c r="A9" s="102" t="inlineStr">
+      <c r="L8" s="94" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="287" t="inlineStr">
         <is>
           <t>Tarjeta iCAI · Todo trabajador puede y debe reportar · Reportar a tiempo evita accidentes · Decreto 1072 de 2015</t>
         </is>
       </c>
-      <c r="B9" s="134" t="n"/>
-      <c r="C9" s="134" t="n"/>
-      <c r="D9" s="134" t="n"/>
-      <c r="E9" s="134" t="n"/>
-      <c r="F9" s="134" t="n"/>
-      <c r="G9" s="134" t="n"/>
-      <c r="H9" s="134" t="n"/>
-      <c r="I9" s="134" t="n"/>
-      <c r="J9" s="134" t="n"/>
-      <c r="K9" s="134" t="n"/>
-      <c r="L9" s="135" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="109">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="B9" s="347" t="n"/>
+      <c r="C9" s="347" t="n"/>
+      <c r="D9" s="347" t="n"/>
+      <c r="E9" s="347" t="n"/>
+      <c r="F9" s="347" t="n"/>
+      <c r="G9" s="347" t="n"/>
+      <c r="H9" s="347" t="n"/>
+      <c r="I9" s="347" t="n"/>
+      <c r="J9" s="347" t="n"/>
+      <c r="K9" s="347" t="n"/>
+      <c r="L9" s="352" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DEL REPORTE</t>
         </is>
       </c>
-      <c r="B10" s="93" t="n"/>
-      <c r="C10" s="93" t="n"/>
-      <c r="D10" s="93" t="n"/>
-      <c r="E10" s="93" t="n"/>
-      <c r="F10" s="93" t="n"/>
-      <c r="G10" s="93" t="n"/>
-      <c r="H10" s="93" t="n"/>
-      <c r="I10" s="93" t="n"/>
-      <c r="J10" s="93" t="n"/>
-      <c r="K10" s="93" t="n"/>
-      <c r="L10" s="94" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" s="109">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="87" t="n"/>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="86" t="n"/>
-      <c r="E11" s="86" t="n"/>
-      <c r="F11" s="86" t="n"/>
-      <c r="G11" s="86" t="n"/>
-      <c r="H11" s="86" t="n"/>
-      <c r="I11" s="86" t="n"/>
-      <c r="J11" s="86" t="n"/>
-      <c r="K11" s="86" t="n"/>
-      <c r="L11" s="87" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" s="109">
-      <c r="A12" s="64" t="inlineStr">
+      <c r="B11" s="89" t="n"/>
+      <c r="C11" s="161" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93" t="n"/>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="93" t="n"/>
+      <c r="L11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="B12" s="87" t="n"/>
-      <c r="C12" s="39" t="n"/>
-      <c r="D12" s="86" t="n"/>
-      <c r="E12" s="86" t="n"/>
-      <c r="F12" s="86" t="n"/>
-      <c r="G12" s="87" t="n"/>
-      <c r="H12" s="64" t="inlineStr">
+      <c r="B12" s="89" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="89" t="n"/>
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I12" s="87" t="n"/>
-      <c r="J12" s="39" t="n"/>
-      <c r="K12" s="86" t="n"/>
-      <c r="L12" s="87" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" s="109">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="I12" s="89" t="n"/>
+      <c r="J12" s="68" t="n"/>
+      <c r="K12" s="93" t="n"/>
+      <c r="L12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" s="127">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Fecha del hallazgo</t>
         </is>
       </c>
-      <c r="B13" s="87" t="n"/>
-      <c r="C13" s="59" t="n"/>
-      <c r="D13" s="64" t="inlineStr">
+      <c r="B13" s="89" t="n"/>
+      <c r="C13" s="69" t="n"/>
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="64" t="inlineStr">
+      <c r="E13" s="69" t="n"/>
+      <c r="F13" s="59" t="inlineStr">
         <is>
           <t>N° de reporte</t>
         </is>
       </c>
-      <c r="G13" s="59" t="n"/>
-      <c r="H13" s="64" t="inlineStr">
+      <c r="G13" s="69" t="n"/>
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Tipo de reporte</t>
         </is>
       </c>
-      <c r="I13" s="87" t="n"/>
-      <c r="J13" s="39" t="n"/>
-      <c r="K13" s="86" t="n"/>
-      <c r="L13" s="87" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" s="109">
-      <c r="A14" s="64" t="inlineStr">
+      <c r="I13" s="89" t="n"/>
+      <c r="J13" s="68" t="n"/>
+      <c r="K13" s="93" t="n"/>
+      <c r="L13" s="89" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" s="127">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>Lugar exacto del hallazgo</t>
         </is>
       </c>
-      <c r="B14" s="87" t="n"/>
-      <c r="C14" s="39" t="n"/>
-      <c r="D14" s="86" t="n"/>
-      <c r="E14" s="86" t="n"/>
-      <c r="F14" s="86" t="n"/>
-      <c r="G14" s="86" t="n"/>
-      <c r="H14" s="86" t="n"/>
-      <c r="I14" s="86" t="n"/>
-      <c r="J14" s="86" t="n"/>
-      <c r="K14" s="86" t="n"/>
-      <c r="L14" s="87" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" s="109">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="B14" s="89" t="n"/>
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="93" t="n"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="93" t="n"/>
+      <c r="H14" s="93" t="n"/>
+      <c r="I14" s="93" t="n"/>
+      <c r="J14" s="93" t="n"/>
+      <c r="K14" s="93" t="n"/>
+      <c r="L14" s="89" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="127">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>Quién reporta</t>
         </is>
       </c>
-      <c r="B15" s="87" t="n"/>
-      <c r="C15" s="39" t="n"/>
-      <c r="D15" s="86" t="n"/>
-      <c r="E15" s="86" t="n"/>
-      <c r="F15" s="86" t="n"/>
-      <c r="G15" s="87" t="n"/>
-      <c r="H15" s="64" t="inlineStr">
+      <c r="B15" s="89" t="n"/>
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="93" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="93" t="n"/>
+      <c r="G15" s="89" t="n"/>
+      <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Cargo / oficio</t>
         </is>
       </c>
-      <c r="I15" s="87" t="n"/>
-      <c r="J15" s="39" t="n"/>
-      <c r="K15" s="86" t="n"/>
-      <c r="L15" s="87" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="109">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="I15" s="89" t="n"/>
+      <c r="J15" s="68" t="n"/>
+      <c r="K15" s="93" t="n"/>
+      <c r="L15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="127">
+      <c r="A16" s="227" t="inlineStr">
         <is>
           <t>2. CLASIFICACIÓN (marque lo que corresponda)</t>
         </is>
       </c>
-      <c r="B16" s="93" t="n"/>
-      <c r="C16" s="93" t="n"/>
-      <c r="D16" s="93" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="93" t="n"/>
-      <c r="H16" s="93" t="n"/>
-      <c r="I16" s="93" t="n"/>
-      <c r="J16" s="93" t="n"/>
-      <c r="K16" s="93" t="n"/>
-      <c r="L16" s="94" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="109">
-      <c r="A17" s="62" t="inlineStr">
+      <c r="L16" s="92" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="127">
+      <c r="A17" s="231" t="inlineStr">
         <is>
           <t>Actos inseguros (lo que hace una persona)</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n"/>
-      <c r="C17" s="86" t="n"/>
-      <c r="D17" s="86" t="n"/>
-      <c r="E17" s="86" t="n"/>
-      <c r="F17" s="86" t="n"/>
-      <c r="G17" s="86" t="n"/>
-      <c r="H17" s="86" t="n"/>
-      <c r="I17" s="86" t="n"/>
-      <c r="J17" s="86" t="n"/>
-      <c r="K17" s="86" t="n"/>
-      <c r="L17" s="87" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="109">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="B17" s="347" t="n"/>
+      <c r="C17" s="347" t="n"/>
+      <c r="D17" s="347" t="n"/>
+      <c r="E17" s="347" t="n"/>
+      <c r="F17" s="347" t="n"/>
+      <c r="G17" s="347" t="n"/>
+      <c r="H17" s="347" t="n"/>
+      <c r="I17" s="347" t="n"/>
+      <c r="J17" s="347" t="n"/>
+      <c r="K17" s="347" t="n"/>
+      <c r="L17" s="358" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" s="127">
+      <c r="A18" s="230" t="inlineStr">
         <is>
           <t>☐ No usar o usar mal los EPP</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n"/>
-      <c r="C18" s="87" t="n"/>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="B18" s="98" t="n"/>
+      <c r="C18" s="97" t="n"/>
+      <c r="D18" s="230" t="inlineStr">
         <is>
           <t>☐ Omitir procedimientos o permisos</t>
         </is>
       </c>
-      <c r="E18" s="86" t="n"/>
-      <c r="F18" s="87" t="n"/>
-      <c r="G18" s="61" t="inlineStr">
+      <c r="E18" s="98" t="n"/>
+      <c r="F18" s="97" t="n"/>
+      <c r="G18" s="230" t="inlineStr">
         <is>
           <t>☐ Trabajar sin ATS o sin autorización</t>
         </is>
       </c>
-      <c r="H18" s="86" t="n"/>
-      <c r="I18" s="87" t="n"/>
-      <c r="J18" s="61" t="inlineStr">
+      <c r="H18" s="98" t="n"/>
+      <c r="I18" s="97" t="n"/>
+      <c r="J18" s="230" t="inlineStr">
         <is>
           <t>☐ Usar herramientas o equipos inadecuados</t>
         </is>
       </c>
-      <c r="K18" s="86" t="n"/>
-      <c r="L18" s="87" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="109">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="K18" s="98" t="n"/>
+      <c r="L18" s="97" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" s="127">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>☐ Trabajar en alturas sin protección</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n"/>
-      <c r="C19" s="87" t="n"/>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="B19" s="93" t="n"/>
+      <c r="C19" s="89" t="n"/>
+      <c r="D19" s="72" t="inlineStr">
         <is>
           <t>☐ Bloquear salidas o rutas de evacuación</t>
         </is>
       </c>
-      <c r="E19" s="86" t="n"/>
-      <c r="F19" s="87" t="n"/>
-      <c r="G19" s="61" t="inlineStr">
+      <c r="E19" s="93" t="n"/>
+      <c r="F19" s="89" t="n"/>
+      <c r="G19" s="72" t="inlineStr">
         <is>
           <t>☐ Cargas o posturas inadecuadas</t>
         </is>
       </c>
-      <c r="H19" s="86" t="n"/>
-      <c r="I19" s="87" t="n"/>
-      <c r="J19" s="61" t="inlineStr">
+      <c r="H19" s="93" t="n"/>
+      <c r="I19" s="89" t="n"/>
+      <c r="J19" s="72" t="inlineStr">
         <is>
           <t>☐ Distracción o uso del celular</t>
         </is>
       </c>
-      <c r="K19" s="86" t="n"/>
-      <c r="L19" s="87" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" s="109">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="K19" s="93" t="n"/>
+      <c r="L19" s="89" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" s="127">
+      <c r="A20" s="234" t="inlineStr">
         <is>
           <t>☐ Bromas o juegos en el área de trabajo</t>
         </is>
       </c>
-      <c r="B20" s="86" t="n"/>
-      <c r="C20" s="87" t="n"/>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="B20" s="104" t="n"/>
+      <c r="C20" s="94" t="n"/>
+      <c r="D20" s="234" t="inlineStr">
         <is>
           <t>☐ Trabajar bajo alcohol o sustancias</t>
         </is>
       </c>
-      <c r="E20" s="86" t="n"/>
-      <c r="F20" s="87" t="n"/>
-      <c r="G20" s="61" t="inlineStr">
+      <c r="E20" s="104" t="n"/>
+      <c r="F20" s="94" t="n"/>
+      <c r="G20" s="234" t="inlineStr">
         <is>
           <t>☐ Manejo inseguro de vehículos</t>
         </is>
       </c>
-      <c r="H20" s="86" t="n"/>
-      <c r="I20" s="87" t="n"/>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="H20" s="104" t="n"/>
+      <c r="I20" s="94" t="n"/>
+      <c r="J20" s="234" t="inlineStr">
         <is>
           <t>☐ Otro acto: ____________</t>
         </is>
       </c>
-      <c r="K20" s="86" t="n"/>
-      <c r="L20" s="87" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="109">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="K20" s="104" t="n"/>
+      <c r="L20" s="94" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="127">
+      <c r="A21" s="231" t="inlineStr">
         <is>
           <t>Condiciones inseguras (lo que hay en el entorno)</t>
         </is>
       </c>
-      <c r="B21" s="86" t="n"/>
-      <c r="C21" s="86" t="n"/>
-      <c r="D21" s="86" t="n"/>
-      <c r="E21" s="86" t="n"/>
-      <c r="F21" s="86" t="n"/>
-      <c r="G21" s="86" t="n"/>
-      <c r="H21" s="86" t="n"/>
-      <c r="I21" s="86" t="n"/>
-      <c r="J21" s="86" t="n"/>
-      <c r="K21" s="86" t="n"/>
-      <c r="L21" s="87" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" s="109">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="B21" s="347" t="n"/>
+      <c r="C21" s="347" t="n"/>
+      <c r="D21" s="347" t="n"/>
+      <c r="E21" s="347" t="n"/>
+      <c r="F21" s="347" t="n"/>
+      <c r="G21" s="347" t="n"/>
+      <c r="H21" s="347" t="n"/>
+      <c r="I21" s="347" t="n"/>
+      <c r="J21" s="347" t="n"/>
+      <c r="K21" s="347" t="n"/>
+      <c r="L21" s="358" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" s="127">
+      <c r="A22" s="230" t="inlineStr">
         <is>
           <t>☐ Desorden o falta de aseo</t>
         </is>
       </c>
-      <c r="B22" s="86" t="n"/>
-      <c r="C22" s="87" t="n"/>
-      <c r="D22" s="61" t="inlineStr">
+      <c r="B22" s="98" t="n"/>
+      <c r="C22" s="97" t="n"/>
+      <c r="D22" s="230" t="inlineStr">
         <is>
           <t>☐ Herramienta o equipo defectuoso</t>
         </is>
       </c>
-      <c r="E22" s="86" t="n"/>
-      <c r="F22" s="87" t="n"/>
-      <c r="G22" s="61" t="inlineStr">
+      <c r="E22" s="98" t="n"/>
+      <c r="F22" s="97" t="n"/>
+      <c r="G22" s="230" t="inlineStr">
         <is>
           <t>☐ Falta de señalización o demarcación</t>
         </is>
       </c>
-      <c r="H22" s="86" t="n"/>
-      <c r="I22" s="87" t="n"/>
-      <c r="J22" s="61" t="inlineStr">
+      <c r="H22" s="98" t="n"/>
+      <c r="I22" s="97" t="n"/>
+      <c r="J22" s="230" t="inlineStr">
         <is>
           <t>☐ Falta de guardas o protecciones</t>
         </is>
       </c>
-      <c r="K22" s="86" t="n"/>
-      <c r="L22" s="87" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" s="109">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="K22" s="98" t="n"/>
+      <c r="L22" s="97" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" s="127">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>☐ Instalación eléctrica deficiente</t>
         </is>
       </c>
-      <c r="B23" s="86" t="n"/>
-      <c r="C23" s="87" t="n"/>
-      <c r="D23" s="61" t="inlineStr">
+      <c r="B23" s="93" t="n"/>
+      <c r="C23" s="89" t="n"/>
+      <c r="D23" s="72" t="inlineStr">
         <is>
           <t>☐ Andamio, escalera o plataforma en mal estado</t>
         </is>
       </c>
-      <c r="E23" s="86" t="n"/>
-      <c r="F23" s="87" t="n"/>
-      <c r="G23" s="61" t="inlineStr">
+      <c r="E23" s="93" t="n"/>
+      <c r="F23" s="89" t="n"/>
+      <c r="G23" s="72" t="inlineStr">
         <is>
           <t>☐ Iluminación o ventilación insuficiente</t>
         </is>
       </c>
-      <c r="H23" s="86" t="n"/>
-      <c r="I23" s="87" t="n"/>
-      <c r="J23" s="61" t="inlineStr">
+      <c r="H23" s="93" t="n"/>
+      <c r="I23" s="89" t="n"/>
+      <c r="J23" s="72" t="inlineStr">
         <is>
           <t>☐ Piso irregular, húmedo o con huecos</t>
         </is>
       </c>
-      <c r="K23" s="86" t="n"/>
-      <c r="L23" s="87" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" s="109">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="K23" s="93" t="n"/>
+      <c r="L23" s="89" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="127">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>☐ Material mal almacenado</t>
         </is>
       </c>
-      <c r="B24" s="86" t="n"/>
-      <c r="C24" s="87" t="n"/>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="B24" s="93" t="n"/>
+      <c r="C24" s="89" t="n"/>
+      <c r="D24" s="72" t="inlineStr">
         <is>
           <t>☐ Fugas o derrames</t>
         </is>
       </c>
-      <c r="E24" s="86" t="n"/>
-      <c r="F24" s="87" t="n"/>
-      <c r="G24" s="61" t="inlineStr">
+      <c r="E24" s="93" t="n"/>
+      <c r="F24" s="89" t="n"/>
+      <c r="G24" s="72" t="inlineStr">
         <is>
           <t>☐ Falta de extintor o de botiquín</t>
         </is>
       </c>
-      <c r="H24" s="86" t="n"/>
-      <c r="I24" s="87" t="n"/>
-      <c r="J24" s="61" t="inlineStr">
+      <c r="H24" s="93" t="n"/>
+      <c r="I24" s="89" t="n"/>
+      <c r="J24" s="72" t="inlineStr">
         <is>
           <t>☐ Otra condición: ____________</t>
         </is>
       </c>
-      <c r="K24" s="86" t="n"/>
-      <c r="L24" s="87" t="n"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="109">
-      <c r="A25" s="71" t="inlineStr">
+      <c r="K24" s="93" t="n"/>
+      <c r="L24" s="89" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="127">
+      <c r="A25" s="137" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN DEL HALLAZGO</t>
         </is>
       </c>
-      <c r="B25" s="93" t="n"/>
-      <c r="C25" s="93" t="n"/>
-      <c r="D25" s="93" t="n"/>
-      <c r="E25" s="93" t="n"/>
-      <c r="F25" s="93" t="n"/>
-      <c r="G25" s="93" t="n"/>
-      <c r="H25" s="93" t="n"/>
-      <c r="I25" s="93" t="n"/>
-      <c r="J25" s="93" t="n"/>
-      <c r="K25" s="93" t="n"/>
-      <c r="L25" s="94" t="n"/>
-    </row>
-    <row r="26" ht="48" customHeight="1" s="109">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="B25" s="98" t="n"/>
+      <c r="C25" s="98" t="n"/>
+      <c r="D25" s="98" t="n"/>
+      <c r="E25" s="98" t="n"/>
+      <c r="F25" s="98" t="n"/>
+      <c r="G25" s="98" t="n"/>
+      <c r="H25" s="98" t="n"/>
+      <c r="I25" s="98" t="n"/>
+      <c r="J25" s="98" t="n"/>
+      <c r="K25" s="98" t="n"/>
+      <c r="L25" s="97" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="127">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>¿Qué se observó?</t>
         </is>
       </c>
-      <c r="B26" s="87" t="n"/>
-      <c r="C26" s="95" t="n"/>
-      <c r="D26" s="86" t="n"/>
-      <c r="E26" s="86" t="n"/>
-      <c r="F26" s="86" t="n"/>
-      <c r="G26" s="86" t="n"/>
-      <c r="H26" s="86" t="n"/>
-      <c r="I26" s="86" t="n"/>
-      <c r="J26" s="86" t="n"/>
-      <c r="K26" s="86" t="n"/>
-      <c r="L26" s="87" t="n"/>
-    </row>
-    <row r="27" ht="34.05" customHeight="1" s="109">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="B26" s="89" t="n"/>
+      <c r="C26" s="100" t="n"/>
+      <c r="D26" s="93" t="n"/>
+      <c r="E26" s="93" t="n"/>
+      <c r="F26" s="93" t="n"/>
+      <c r="G26" s="93" t="n"/>
+      <c r="H26" s="93" t="n"/>
+      <c r="I26" s="93" t="n"/>
+      <c r="J26" s="93" t="n"/>
+      <c r="K26" s="93" t="n"/>
+      <c r="L26" s="89" t="n"/>
+    </row>
+    <row r="27" ht="34.05" customHeight="1" s="127">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>Posible consecuencia</t>
         </is>
       </c>
-      <c r="B27" s="87" t="n"/>
-      <c r="C27" s="95" t="n"/>
-      <c r="D27" s="86" t="n"/>
-      <c r="E27" s="86" t="n"/>
-      <c r="F27" s="86" t="n"/>
-      <c r="G27" s="86" t="n"/>
-      <c r="H27" s="86" t="n"/>
-      <c r="I27" s="86" t="n"/>
-      <c r="J27" s="86" t="n"/>
-      <c r="K27" s="86" t="n"/>
-      <c r="L27" s="87" t="n"/>
-    </row>
-    <row r="28" ht="21" customHeight="1" s="109">
-      <c r="A28" s="64" t="inlineStr">
+      <c r="B27" s="89" t="n"/>
+      <c r="C27" s="100" t="n"/>
+      <c r="D27" s="93" t="n"/>
+      <c r="E27" s="93" t="n"/>
+      <c r="F27" s="93" t="n"/>
+      <c r="G27" s="93" t="n"/>
+      <c r="H27" s="93" t="n"/>
+      <c r="I27" s="93" t="n"/>
+      <c r="J27" s="93" t="n"/>
+      <c r="K27" s="93" t="n"/>
+      <c r="L27" s="89" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1" s="127">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>Persona(s) involucrada(s) (opcional)</t>
         </is>
       </c>
-      <c r="B28" s="87" t="n"/>
-      <c r="C28" s="39" t="n"/>
-      <c r="D28" s="86" t="n"/>
-      <c r="E28" s="86" t="n"/>
-      <c r="F28" s="86" t="n"/>
-      <c r="G28" s="86" t="n"/>
-      <c r="H28" s="86" t="n"/>
-      <c r="I28" s="86" t="n"/>
-      <c r="J28" s="86" t="n"/>
-      <c r="K28" s="86" t="n"/>
-      <c r="L28" s="87" t="n"/>
-    </row>
-    <row r="29" ht="21" customHeight="1" s="109">
-      <c r="A29" s="64" t="inlineStr">
+      <c r="B28" s="89" t="n"/>
+      <c r="C28" s="68" t="n"/>
+      <c r="D28" s="93" t="n"/>
+      <c r="E28" s="93" t="n"/>
+      <c r="F28" s="93" t="n"/>
+      <c r="G28" s="93" t="n"/>
+      <c r="H28" s="93" t="n"/>
+      <c r="I28" s="93" t="n"/>
+      <c r="J28" s="93" t="n"/>
+      <c r="K28" s="93" t="n"/>
+      <c r="L28" s="89" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1" s="127">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>Probabilidad</t>
         </is>
       </c>
-      <c r="B29" s="87" t="n"/>
-      <c r="C29" s="59" t="n"/>
-      <c r="D29" s="87" t="n"/>
-      <c r="E29" s="64" t="inlineStr">
+      <c r="B29" s="89" t="n"/>
+      <c r="C29" s="69" t="n"/>
+      <c r="D29" s="89" t="n"/>
+      <c r="E29" s="59" t="inlineStr">
         <is>
           <t>Severidad</t>
         </is>
       </c>
-      <c r="F29" s="87" t="n"/>
-      <c r="G29" s="59" t="n"/>
-      <c r="H29" s="87" t="n"/>
-      <c r="I29" s="64" t="inlineStr">
+      <c r="F29" s="89" t="n"/>
+      <c r="G29" s="69" t="n"/>
+      <c r="H29" s="89" t="n"/>
+      <c r="I29" s="59" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
-      <c r="J29" s="87" t="n"/>
-      <c r="K29" s="59" t="n"/>
-      <c r="L29" s="87" t="n"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="109">
-      <c r="A30" s="71" t="inlineStr">
+      <c r="J29" s="89" t="n"/>
+      <c r="K29" s="69" t="n"/>
+      <c r="L29" s="89" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="127">
+      <c r="A30" s="137" t="inlineStr">
         <is>
           <t>4. ACCIÓN INMEDIATA Y RECOMENDACIÓN</t>
         </is>
       </c>
-      <c r="B30" s="93" t="n"/>
-      <c r="C30" s="93" t="n"/>
-      <c r="D30" s="93" t="n"/>
-      <c r="E30" s="93" t="n"/>
-      <c r="F30" s="93" t="n"/>
-      <c r="G30" s="93" t="n"/>
-      <c r="H30" s="93" t="n"/>
-      <c r="I30" s="93" t="n"/>
-      <c r="J30" s="93" t="n"/>
-      <c r="K30" s="93" t="n"/>
-      <c r="L30" s="94" t="n"/>
-    </row>
-    <row r="31" ht="34.05" customHeight="1" s="109">
-      <c r="A31" s="64" t="inlineStr">
+      <c r="B30" s="98" t="n"/>
+      <c r="C30" s="98" t="n"/>
+      <c r="D30" s="98" t="n"/>
+      <c r="E30" s="98" t="n"/>
+      <c r="F30" s="98" t="n"/>
+      <c r="G30" s="98" t="n"/>
+      <c r="H30" s="98" t="n"/>
+      <c r="I30" s="98" t="n"/>
+      <c r="J30" s="98" t="n"/>
+      <c r="K30" s="98" t="n"/>
+      <c r="L30" s="97" t="n"/>
+    </row>
+    <row r="31" ht="34.05" customHeight="1" s="127">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>Acción inmediata tomada</t>
         </is>
       </c>
-      <c r="B31" s="87" t="n"/>
-      <c r="C31" s="95" t="n"/>
-      <c r="D31" s="86" t="n"/>
-      <c r="E31" s="86" t="n"/>
-      <c r="F31" s="86" t="n"/>
-      <c r="G31" s="86" t="n"/>
-      <c r="H31" s="86" t="n"/>
-      <c r="I31" s="86" t="n"/>
-      <c r="J31" s="86" t="n"/>
-      <c r="K31" s="86" t="n"/>
-      <c r="L31" s="87" t="n"/>
-    </row>
-    <row r="32" ht="34.05" customHeight="1" s="109">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="B31" s="89" t="n"/>
+      <c r="C31" s="100" t="n"/>
+      <c r="D31" s="93" t="n"/>
+      <c r="E31" s="93" t="n"/>
+      <c r="F31" s="93" t="n"/>
+      <c r="G31" s="93" t="n"/>
+      <c r="H31" s="93" t="n"/>
+      <c r="I31" s="93" t="n"/>
+      <c r="J31" s="93" t="n"/>
+      <c r="K31" s="93" t="n"/>
+      <c r="L31" s="89" t="n"/>
+    </row>
+    <row r="32" ht="34.05" customHeight="1" s="127">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>Recomendación o acción correctiva propuesta</t>
         </is>
       </c>
-      <c r="B32" s="87" t="n"/>
-      <c r="C32" s="95" t="n"/>
-      <c r="D32" s="86" t="n"/>
-      <c r="E32" s="86" t="n"/>
-      <c r="F32" s="86" t="n"/>
-      <c r="G32" s="86" t="n"/>
-      <c r="H32" s="86" t="n"/>
-      <c r="I32" s="86" t="n"/>
-      <c r="J32" s="86" t="n"/>
-      <c r="K32" s="86" t="n"/>
-      <c r="L32" s="87" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1" s="109">
-      <c r="A33" s="64" t="inlineStr">
+      <c r="B32" s="89" t="n"/>
+      <c r="C32" s="100" t="n"/>
+      <c r="D32" s="93" t="n"/>
+      <c r="E32" s="93" t="n"/>
+      <c r="F32" s="93" t="n"/>
+      <c r="G32" s="93" t="n"/>
+      <c r="H32" s="93" t="n"/>
+      <c r="I32" s="93" t="n"/>
+      <c r="J32" s="93" t="n"/>
+      <c r="K32" s="93" t="n"/>
+      <c r="L32" s="89" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1" s="127">
+      <c r="A33" s="59" t="inlineStr">
         <is>
           <t>Responsable de la corrección</t>
         </is>
       </c>
-      <c r="B33" s="87" t="n"/>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="86" t="n"/>
-      <c r="E33" s="86" t="n"/>
-      <c r="F33" s="86" t="n"/>
-      <c r="G33" s="87" t="n"/>
-      <c r="H33" s="64" t="inlineStr">
+      <c r="B33" s="89" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="93" t="n"/>
+      <c r="E33" s="93" t="n"/>
+      <c r="F33" s="93" t="n"/>
+      <c r="G33" s="89" t="n"/>
+      <c r="H33" s="59" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
       </c>
-      <c r="I33" s="87" t="n"/>
-      <c r="J33" s="59" t="n"/>
-      <c r="K33" s="86" t="n"/>
-      <c r="L33" s="87" t="n"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="109">
-      <c r="A34" s="71" t="inlineStr">
+      <c r="I33" s="89" t="n"/>
+      <c r="J33" s="69" t="n"/>
+      <c r="K33" s="93" t="n"/>
+      <c r="L33" s="89" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="127">
+      <c r="A34" s="137" t="inlineStr">
         <is>
           <t>5. EVIDENCIA FOTOGRÁFICA</t>
         </is>
       </c>
-      <c r="B34" s="93" t="n"/>
-      <c r="C34" s="93" t="n"/>
-      <c r="D34" s="93" t="n"/>
-      <c r="E34" s="93" t="n"/>
-      <c r="F34" s="93" t="n"/>
-      <c r="G34" s="93" t="n"/>
-      <c r="H34" s="93" t="n"/>
-      <c r="I34" s="93" t="n"/>
-      <c r="J34" s="93" t="n"/>
-      <c r="K34" s="93" t="n"/>
-      <c r="L34" s="94" t="n"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="109">
-      <c r="A35" s="111" t="n"/>
-      <c r="B35" s="96" t="n"/>
-      <c r="C35" s="96" t="n"/>
-      <c r="D35" s="96" t="n"/>
-      <c r="E35" s="96" t="n"/>
-      <c r="F35" s="97" t="n"/>
-      <c r="G35" s="111" t="n"/>
-      <c r="H35" s="96" t="n"/>
-      <c r="I35" s="96" t="n"/>
-      <c r="J35" s="96" t="n"/>
-      <c r="K35" s="96" t="n"/>
-      <c r="L35" s="97" t="n"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="109">
-      <c r="A36" s="98" t="n"/>
-      <c r="F36" s="100" t="n"/>
-      <c r="G36" s="98" t="n"/>
-      <c r="L36" s="100" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="109">
-      <c r="A37" s="98" t="n"/>
-      <c r="F37" s="100" t="n"/>
-      <c r="G37" s="98" t="n"/>
-      <c r="L37" s="100" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="109">
-      <c r="A38" s="98" t="n"/>
-      <c r="F38" s="100" t="n"/>
-      <c r="G38" s="98" t="n"/>
-      <c r="L38" s="100" t="n"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="109">
-      <c r="A39" s="98" t="n"/>
-      <c r="F39" s="100" t="n"/>
-      <c r="G39" s="98" t="n"/>
-      <c r="L39" s="100" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="109">
-      <c r="A40" s="98" t="n"/>
-      <c r="F40" s="100" t="n"/>
-      <c r="G40" s="98" t="n"/>
-      <c r="L40" s="100" t="n"/>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" s="109">
-      <c r="A41" s="98" t="n"/>
-      <c r="F41" s="100" t="n"/>
-      <c r="G41" s="98" t="n"/>
-      <c r="L41" s="100" t="n"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="109">
-      <c r="A42" s="98" t="n"/>
-      <c r="F42" s="100" t="n"/>
-      <c r="G42" s="98" t="n"/>
-      <c r="L42" s="100" t="n"/>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" s="109">
-      <c r="A43" s="98" t="n"/>
-      <c r="F43" s="100" t="n"/>
-      <c r="G43" s="98" t="n"/>
-      <c r="L43" s="100" t="n"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1" s="109">
-      <c r="A44" s="98" t="n"/>
-      <c r="F44" s="100" t="n"/>
-      <c r="G44" s="98" t="n"/>
-      <c r="L44" s="100" t="n"/>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="109">
-      <c r="A45" s="98" t="n"/>
-      <c r="F45" s="100" t="n"/>
-      <c r="G45" s="98" t="n"/>
-      <c r="L45" s="100" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="109">
-      <c r="A46" s="98" t="n"/>
-      <c r="F46" s="100" t="n"/>
-      <c r="G46" s="98" t="n"/>
-      <c r="L46" s="100" t="n"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="109">
-      <c r="A47" s="98" t="n"/>
-      <c r="F47" s="100" t="n"/>
-      <c r="G47" s="98" t="n"/>
-      <c r="L47" s="100" t="n"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="109">
-      <c r="A48" s="98" t="n"/>
-      <c r="F48" s="100" t="n"/>
-      <c r="G48" s="98" t="n"/>
-      <c r="L48" s="100" t="n"/>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="109">
-      <c r="A49" s="98" t="n"/>
-      <c r="F49" s="100" t="n"/>
-      <c r="G49" s="98" t="n"/>
-      <c r="L49" s="100" t="n"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="109">
-      <c r="A50" s="101" t="n"/>
-      <c r="B50" s="93" t="n"/>
-      <c r="C50" s="93" t="n"/>
-      <c r="D50" s="93" t="n"/>
-      <c r="E50" s="93" t="n"/>
-      <c r="F50" s="94" t="n"/>
-      <c r="G50" s="101" t="n"/>
-      <c r="H50" s="93" t="n"/>
-      <c r="I50" s="93" t="n"/>
-      <c r="J50" s="93" t="n"/>
-      <c r="K50" s="93" t="n"/>
-      <c r="L50" s="94" t="n"/>
-    </row>
-    <row r="51" ht="18" customHeight="1" s="109">
-      <c r="A51" s="112" t="inlineStr">
+      <c r="B34" s="98" t="n"/>
+      <c r="C34" s="98" t="n"/>
+      <c r="D34" s="98" t="n"/>
+      <c r="E34" s="98" t="n"/>
+      <c r="F34" s="98" t="n"/>
+      <c r="G34" s="98" t="n"/>
+      <c r="H34" s="98" t="n"/>
+      <c r="I34" s="98" t="n"/>
+      <c r="J34" s="98" t="n"/>
+      <c r="K34" s="98" t="n"/>
+      <c r="L34" s="97" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="127">
+      <c r="A35" s="129" t="n"/>
+      <c r="B35" s="104" t="n"/>
+      <c r="C35" s="104" t="n"/>
+      <c r="D35" s="104" t="n"/>
+      <c r="E35" s="104" t="n"/>
+      <c r="F35" s="94" t="n"/>
+      <c r="G35" s="129" t="n"/>
+      <c r="H35" s="104" t="n"/>
+      <c r="I35" s="104" t="n"/>
+      <c r="J35" s="104" t="n"/>
+      <c r="K35" s="104" t="n"/>
+      <c r="L35" s="94" t="n"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="127">
+      <c r="A36" s="95" t="n"/>
+      <c r="F36" s="92" t="n"/>
+      <c r="G36" s="95" t="n"/>
+      <c r="L36" s="92" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="127">
+      <c r="A37" s="95" t="n"/>
+      <c r="F37" s="92" t="n"/>
+      <c r="G37" s="95" t="n"/>
+      <c r="L37" s="92" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="127">
+      <c r="A38" s="95" t="n"/>
+      <c r="F38" s="92" t="n"/>
+      <c r="G38" s="95" t="n"/>
+      <c r="L38" s="92" t="n"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="127">
+      <c r="A39" s="95" t="n"/>
+      <c r="F39" s="92" t="n"/>
+      <c r="G39" s="95" t="n"/>
+      <c r="L39" s="92" t="n"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="127">
+      <c r="A40" s="95" t="n"/>
+      <c r="F40" s="92" t="n"/>
+      <c r="G40" s="95" t="n"/>
+      <c r="L40" s="92" t="n"/>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="127">
+      <c r="A41" s="95" t="n"/>
+      <c r="F41" s="92" t="n"/>
+      <c r="G41" s="95" t="n"/>
+      <c r="L41" s="92" t="n"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="127">
+      <c r="A42" s="95" t="n"/>
+      <c r="F42" s="92" t="n"/>
+      <c r="G42" s="95" t="n"/>
+      <c r="L42" s="92" t="n"/>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="127">
+      <c r="A43" s="95" t="n"/>
+      <c r="F43" s="92" t="n"/>
+      <c r="G43" s="95" t="n"/>
+      <c r="L43" s="92" t="n"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="127">
+      <c r="A44" s="95" t="n"/>
+      <c r="F44" s="92" t="n"/>
+      <c r="G44" s="95" t="n"/>
+      <c r="L44" s="92" t="n"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="127">
+      <c r="A45" s="95" t="n"/>
+      <c r="F45" s="92" t="n"/>
+      <c r="G45" s="95" t="n"/>
+      <c r="L45" s="92" t="n"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="127">
+      <c r="A46" s="95" t="n"/>
+      <c r="F46" s="92" t="n"/>
+      <c r="G46" s="95" t="n"/>
+      <c r="L46" s="92" t="n"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="127">
+      <c r="A47" s="95" t="n"/>
+      <c r="F47" s="92" t="n"/>
+      <c r="G47" s="95" t="n"/>
+      <c r="L47" s="92" t="n"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="127">
+      <c r="A48" s="95" t="n"/>
+      <c r="F48" s="92" t="n"/>
+      <c r="G48" s="95" t="n"/>
+      <c r="L48" s="92" t="n"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="127">
+      <c r="A49" s="95" t="n"/>
+      <c r="F49" s="92" t="n"/>
+      <c r="G49" s="95" t="n"/>
+      <c r="L49" s="92" t="n"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" s="127">
+      <c r="A50" s="96" t="n"/>
+      <c r="B50" s="98" t="n"/>
+      <c r="C50" s="98" t="n"/>
+      <c r="D50" s="98" t="n"/>
+      <c r="E50" s="98" t="n"/>
+      <c r="F50" s="97" t="n"/>
+      <c r="G50" s="96" t="n"/>
+      <c r="H50" s="98" t="n"/>
+      <c r="I50" s="98" t="n"/>
+      <c r="J50" s="98" t="n"/>
+      <c r="K50" s="98" t="n"/>
+      <c r="L50" s="97" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="127">
+      <c r="A51" s="130" t="inlineStr">
         <is>
           <t>ANTES — el acto o la condición observada</t>
         </is>
       </c>
-      <c r="B51" s="86" t="n"/>
-      <c r="C51" s="86" t="n"/>
-      <c r="D51" s="86" t="n"/>
-      <c r="E51" s="86" t="n"/>
-      <c r="F51" s="87" t="n"/>
-      <c r="G51" s="112" t="inlineStr">
+      <c r="B51" s="93" t="n"/>
+      <c r="C51" s="93" t="n"/>
+      <c r="D51" s="93" t="n"/>
+      <c r="E51" s="93" t="n"/>
+      <c r="F51" s="89" t="n"/>
+      <c r="G51" s="130" t="inlineStr">
         <is>
           <t>DESPUÉS — ya corregido (cuando aplique)</t>
         </is>
       </c>
-      <c r="H51" s="86" t="n"/>
-      <c r="I51" s="86" t="n"/>
-      <c r="J51" s="86" t="n"/>
-      <c r="K51" s="86" t="n"/>
-      <c r="L51" s="87" t="n"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" s="109">
-      <c r="A52" s="71" t="inlineStr">
+      <c r="H51" s="93" t="n"/>
+      <c r="I51" s="93" t="n"/>
+      <c r="J51" s="93" t="n"/>
+      <c r="K51" s="93" t="n"/>
+      <c r="L51" s="89" t="n"/>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" s="127">
+      <c r="A52" s="137" t="inlineStr">
         <is>
           <t>6. SEGUIMIENTO Y CIERRE</t>
         </is>
       </c>
-      <c r="B52" s="93" t="n"/>
-      <c r="C52" s="93" t="n"/>
-      <c r="D52" s="93" t="n"/>
-      <c r="E52" s="93" t="n"/>
-      <c r="F52" s="93" t="n"/>
-      <c r="G52" s="93" t="n"/>
-      <c r="H52" s="93" t="n"/>
-      <c r="I52" s="93" t="n"/>
-      <c r="J52" s="93" t="n"/>
-      <c r="K52" s="93" t="n"/>
-      <c r="L52" s="94" t="n"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" s="109">
-      <c r="A53" s="64" t="inlineStr">
+      <c r="B52" s="98" t="n"/>
+      <c r="C52" s="98" t="n"/>
+      <c r="D52" s="98" t="n"/>
+      <c r="E52" s="98" t="n"/>
+      <c r="F52" s="98" t="n"/>
+      <c r="G52" s="98" t="n"/>
+      <c r="H52" s="98" t="n"/>
+      <c r="I52" s="98" t="n"/>
+      <c r="J52" s="98" t="n"/>
+      <c r="K52" s="98" t="n"/>
+      <c r="L52" s="97" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" s="127">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>¿Quedó corregido?</t>
         </is>
       </c>
-      <c r="B53" s="87" t="n"/>
-      <c r="C53" s="59" t="n"/>
-      <c r="D53" s="87" t="n"/>
-      <c r="E53" s="64" t="inlineStr">
+      <c r="B53" s="89" t="n"/>
+      <c r="C53" s="69" t="n"/>
+      <c r="D53" s="89" t="n"/>
+      <c r="E53" s="59" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
-      <c r="F53" s="87" t="n"/>
-      <c r="G53" s="59" t="n"/>
-      <c r="H53" s="87" t="n"/>
-      <c r="I53" s="64" t="inlineStr">
+      <c r="F53" s="89" t="n"/>
+      <c r="G53" s="69" t="n"/>
+      <c r="H53" s="89" t="n"/>
+      <c r="I53" s="59" t="inlineStr">
         <is>
           <t>Verificó el cierre</t>
         </is>
       </c>
-      <c r="J53" s="87" t="n"/>
-      <c r="K53" s="39" t="n"/>
-      <c r="L53" s="87" t="n"/>
-    </row>
-    <row r="54" ht="30" customHeight="1" s="109">
-      <c r="A54" s="64" t="inlineStr">
+      <c r="J53" s="89" t="n"/>
+      <c r="K53" s="68" t="n"/>
+      <c r="L53" s="89" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" s="127">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>Observaciones del cierre</t>
         </is>
       </c>
-      <c r="B54" s="87" t="n"/>
-      <c r="C54" s="95" t="n"/>
-      <c r="D54" s="86" t="n"/>
-      <c r="E54" s="86" t="n"/>
-      <c r="F54" s="86" t="n"/>
-      <c r="G54" s="86" t="n"/>
-      <c r="H54" s="86" t="n"/>
-      <c r="I54" s="86" t="n"/>
-      <c r="J54" s="86" t="n"/>
-      <c r="K54" s="86" t="n"/>
-      <c r="L54" s="87" t="n"/>
-    </row>
-    <row r="55" ht="16.5" customHeight="1" s="109">
-      <c r="A55" s="71" t="inlineStr">
+      <c r="B54" s="89" t="n"/>
+      <c r="C54" s="100" t="n"/>
+      <c r="D54" s="93" t="n"/>
+      <c r="E54" s="93" t="n"/>
+      <c r="F54" s="93" t="n"/>
+      <c r="G54" s="93" t="n"/>
+      <c r="H54" s="93" t="n"/>
+      <c r="I54" s="93" t="n"/>
+      <c r="J54" s="93" t="n"/>
+      <c r="K54" s="93" t="n"/>
+      <c r="L54" s="89" t="n"/>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" s="127">
+      <c r="A55" s="227" t="inlineStr">
         <is>
           <t>7. FIRMAS</t>
         </is>
       </c>
-      <c r="B55" s="93" t="n"/>
-      <c r="C55" s="93" t="n"/>
-      <c r="D55" s="93" t="n"/>
-      <c r="E55" s="93" t="n"/>
-      <c r="F55" s="93" t="n"/>
-      <c r="G55" s="93" t="n"/>
-      <c r="H55" s="93" t="n"/>
-      <c r="I55" s="93" t="n"/>
-      <c r="J55" s="93" t="n"/>
-      <c r="K55" s="93" t="n"/>
-      <c r="L55" s="94" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1" s="109">
-      <c r="A56" s="42" t="inlineStr">
+      <c r="L55" s="92" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="127">
+      <c r="A56" s="237" t="inlineStr">
         <is>
           <t>QUIEN REPORTA</t>
         </is>
       </c>
-      <c r="B56" s="86" t="n"/>
-      <c r="C56" s="86" t="n"/>
-      <c r="D56" s="87" t="n"/>
-      <c r="E56" s="42" t="inlineStr">
+      <c r="B56" s="347" t="n"/>
+      <c r="C56" s="347" t="n"/>
+      <c r="D56" s="358" t="n"/>
+      <c r="E56" s="240" t="inlineStr">
         <is>
           <t>RECIBE — RESPONSABLE SST / RESIDENTE</t>
         </is>
       </c>
-      <c r="F56" s="86" t="n"/>
-      <c r="G56" s="86" t="n"/>
-      <c r="H56" s="87" t="n"/>
-      <c r="I56" s="42" t="inlineStr">
+      <c r="F56" s="347" t="n"/>
+      <c r="G56" s="347" t="n"/>
+      <c r="H56" s="358" t="n"/>
+      <c r="I56" s="240" t="inlineStr">
         <is>
           <t>VERIFICA EL CIERRE</t>
         </is>
       </c>
-      <c r="J56" s="86" t="n"/>
-      <c r="K56" s="86" t="n"/>
-      <c r="L56" s="87" t="n"/>
-    </row>
-    <row r="57" ht="42" customHeight="1" s="109">
-      <c r="A57" s="38" t="inlineStr">
+      <c r="J56" s="347" t="n"/>
+      <c r="K56" s="347" t="n"/>
+      <c r="L56" s="358" t="n"/>
+    </row>
+    <row r="57" ht="42" customHeight="1" s="127">
+      <c r="A57" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B57" s="87" t="n"/>
-      <c r="C57" s="39" t="n"/>
-      <c r="D57" s="87" t="n"/>
-      <c r="E57" s="38" t="inlineStr">
+      <c r="B57" s="97" t="n"/>
+      <c r="C57" s="301" t="n"/>
+      <c r="D57" s="97" t="n"/>
+      <c r="E57" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F57" s="87" t="n"/>
-      <c r="G57" s="39" t="n"/>
-      <c r="H57" s="87" t="n"/>
-      <c r="I57" s="38" t="inlineStr">
+      <c r="F57" s="97" t="n"/>
+      <c r="G57" s="301" t="n"/>
+      <c r="H57" s="97" t="n"/>
+      <c r="I57" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="J57" s="87" t="n"/>
-      <c r="K57" s="39" t="n"/>
-      <c r="L57" s="87" t="n"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" s="109">
-      <c r="A58" s="38" t="inlineStr">
+      <c r="J57" s="97" t="n"/>
+      <c r="K57" s="301" t="n"/>
+      <c r="L57" s="97" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" s="127">
+      <c r="A58" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B58" s="87" t="n"/>
-      <c r="C58" s="39" t="n"/>
-      <c r="D58" s="87" t="n"/>
-      <c r="E58" s="38" t="inlineStr">
+      <c r="B58" s="89" t="n"/>
+      <c r="C58" s="68" t="n"/>
+      <c r="D58" s="89" t="n"/>
+      <c r="E58" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="F58" s="87" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="87" t="n"/>
-      <c r="I58" s="38" t="inlineStr">
+      <c r="F58" s="89" t="n"/>
+      <c r="G58" s="68" t="n"/>
+      <c r="H58" s="89" t="n"/>
+      <c r="I58" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="J58" s="87" t="n"/>
-      <c r="K58" s="39" t="n"/>
-      <c r="L58" s="87" t="n"/>
-    </row>
-    <row r="59" ht="21" customHeight="1" s="109">
-      <c r="A59" s="38" t="inlineStr">
+      <c r="J58" s="89" t="n"/>
+      <c r="K58" s="68" t="n"/>
+      <c r="L58" s="89" t="n"/>
+    </row>
+    <row r="59" ht="21" customHeight="1" s="127">
+      <c r="A59" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B59" s="87" t="n"/>
-      <c r="C59" s="39" t="n"/>
-      <c r="D59" s="87" t="n"/>
-      <c r="E59" s="38" t="inlineStr">
+      <c r="B59" s="89" t="n"/>
+      <c r="C59" s="68" t="n"/>
+      <c r="D59" s="89" t="n"/>
+      <c r="E59" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="F59" s="87" t="n"/>
-      <c r="G59" s="39" t="n"/>
-      <c r="H59" s="87" t="n"/>
-      <c r="I59" s="38" t="inlineStr">
+      <c r="F59" s="89" t="n"/>
+      <c r="G59" s="68" t="n"/>
+      <c r="H59" s="89" t="n"/>
+      <c r="I59" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="J59" s="87" t="n"/>
-      <c r="K59" s="39" t="n"/>
-      <c r="L59" s="87" t="n"/>
+      <c r="J59" s="89" t="n"/>
+      <c r="K59" s="68" t="n"/>
+      <c r="L59" s="89" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="G60" s="88">
+      <c r="G60" s="105">
         <f>K5</f>
         <v/>
       </c>

--- a/public/plantilla-actos-condiciones.xlsx
+++ b/public/plantilla-actos-condiciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iCAI" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,6 +297,20 @@
       <color rgb="FF0B1F33"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1024,7 +1039,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1943,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2438,8 +2519,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="15.77734375" customWidth="1" style="127" min="1" max="2"/>
+    <col width="13" customWidth="1" style="127" min="2" max="2"/>
     <col width="13" customWidth="1" style="127" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="127" min="4" max="8"/>
+    <col width="13" customWidth="1" style="127" min="5" max="5"/>
+    <col width="13" customWidth="1" style="127" min="6" max="6"/>
+    <col width="13" customWidth="1" style="127" min="7" max="7"/>
+    <col width="13" customWidth="1" style="127" min="8" max="8"/>
     <col width="10" customWidth="1" style="127" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="127" min="10" max="10"/>
     <col width="12" customWidth="1" style="127" min="11" max="11"/>
@@ -2603,16 +2689,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="161" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="360" t="n"/>
+      <c r="D11" s="361" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="361" t="n"/>
+      <c r="H11" s="361" t="n"/>
+      <c r="I11" s="361" t="n"/>
+      <c r="J11" s="361" t="n"/>
+      <c r="K11" s="361" t="n"/>
+      <c r="L11" s="362" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2621,20 +2707,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="363" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="362" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="363" t="n"/>
+      <c r="K12" s="361" t="n"/>
+      <c r="L12" s="362" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2643,28 +2729,28 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
+      <c r="C13" s="364" t="n"/>
       <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="E13" s="69" t="n"/>
+      <c r="E13" s="364" t="n"/>
       <c r="F13" s="59" t="inlineStr">
         <is>
           <t>N° de reporte</t>
         </is>
       </c>
-      <c r="G13" s="69" t="n"/>
+      <c r="G13" s="364" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Tipo de reporte</t>
         </is>
       </c>
       <c r="I13" s="89" t="n"/>
-      <c r="J13" s="68" t="n"/>
-      <c r="K13" s="93" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="J13" s="363" t="n"/>
+      <c r="K13" s="361" t="n"/>
+      <c r="L13" s="362" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2673,16 +2759,16 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="93" t="n"/>
-      <c r="E14" s="93" t="n"/>
-      <c r="F14" s="93" t="n"/>
-      <c r="G14" s="93" t="n"/>
-      <c r="H14" s="93" t="n"/>
-      <c r="I14" s="93" t="n"/>
-      <c r="J14" s="93" t="n"/>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="C14" s="363" t="n"/>
+      <c r="D14" s="361" t="n"/>
+      <c r="E14" s="361" t="n"/>
+      <c r="F14" s="361" t="n"/>
+      <c r="G14" s="361" t="n"/>
+      <c r="H14" s="361" t="n"/>
+      <c r="I14" s="361" t="n"/>
+      <c r="J14" s="361" t="n"/>
+      <c r="K14" s="361" t="n"/>
+      <c r="L14" s="362" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2691,20 +2777,20 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="93" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="89" t="n"/>
+      <c r="C15" s="363" t="n"/>
+      <c r="D15" s="361" t="n"/>
+      <c r="E15" s="361" t="n"/>
+      <c r="F15" s="361" t="n"/>
+      <c r="G15" s="362" t="n"/>
       <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Cargo / oficio</t>
         </is>
       </c>
       <c r="I15" s="89" t="n"/>
-      <c r="J15" s="68" t="n"/>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="J15" s="363" t="n"/>
+      <c r="K15" s="361" t="n"/>
+      <c r="L15" s="362" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="127">
       <c r="A16" s="227" t="inlineStr">
@@ -2732,29 +2818,29 @@
       <c r="K17" s="347" t="n"/>
       <c r="L17" s="358" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1" s="127">
-      <c r="A18" s="230" t="inlineStr">
+    <row r="18" ht="29" customHeight="1" s="127">
+      <c r="A18" s="365" t="inlineStr">
         <is>
           <t>☐ No usar o usar mal los EPP</t>
         </is>
       </c>
       <c r="B18" s="98" t="n"/>
       <c r="C18" s="97" t="n"/>
-      <c r="D18" s="230" t="inlineStr">
+      <c r="D18" s="365" t="inlineStr">
         <is>
           <t>☐ Omitir procedimientos o permisos</t>
         </is>
       </c>
       <c r="E18" s="98" t="n"/>
       <c r="F18" s="97" t="n"/>
-      <c r="G18" s="230" t="inlineStr">
+      <c r="G18" s="365" t="inlineStr">
         <is>
           <t>☐ Trabajar sin ATS o sin autorización</t>
         </is>
       </c>
       <c r="H18" s="98" t="n"/>
       <c r="I18" s="97" t="n"/>
-      <c r="J18" s="230" t="inlineStr">
+      <c r="J18" s="365" t="inlineStr">
         <is>
           <t>☐ Usar herramientas o equipos inadecuados</t>
         </is>
@@ -2763,28 +2849,28 @@
       <c r="L18" s="97" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1" s="127">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="366" t="inlineStr">
         <is>
           <t>☐ Trabajar en alturas sin protección</t>
         </is>
       </c>
       <c r="B19" s="93" t="n"/>
       <c r="C19" s="89" t="n"/>
-      <c r="D19" s="72" t="inlineStr">
+      <c r="D19" s="366" t="inlineStr">
         <is>
           <t>☐ Bloquear salidas o rutas de evacuación</t>
         </is>
       </c>
       <c r="E19" s="93" t="n"/>
       <c r="F19" s="89" t="n"/>
-      <c r="G19" s="72" t="inlineStr">
+      <c r="G19" s="366" t="inlineStr">
         <is>
           <t>☐ Cargas o posturas inadecuadas</t>
         </is>
       </c>
       <c r="H19" s="93" t="n"/>
       <c r="I19" s="89" t="n"/>
-      <c r="J19" s="72" t="inlineStr">
+      <c r="J19" s="366" t="inlineStr">
         <is>
           <t>☐ Distracción o uso del celular</t>
         </is>
@@ -2793,28 +2879,28 @@
       <c r="L19" s="89" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1" s="127">
-      <c r="A20" s="234" t="inlineStr">
+      <c r="A20" s="367" t="inlineStr">
         <is>
           <t>☐ Bromas o juegos en el área de trabajo</t>
         </is>
       </c>
       <c r="B20" s="104" t="n"/>
       <c r="C20" s="94" t="n"/>
-      <c r="D20" s="234" t="inlineStr">
+      <c r="D20" s="367" t="inlineStr">
         <is>
           <t>☐ Trabajar bajo alcohol o sustancias</t>
         </is>
       </c>
       <c r="E20" s="104" t="n"/>
       <c r="F20" s="94" t="n"/>
-      <c r="G20" s="234" t="inlineStr">
+      <c r="G20" s="367" t="inlineStr">
         <is>
           <t>☐ Manejo inseguro de vehículos</t>
         </is>
       </c>
       <c r="H20" s="104" t="n"/>
       <c r="I20" s="94" t="n"/>
-      <c r="J20" s="234" t="inlineStr">
+      <c r="J20" s="367" t="inlineStr">
         <is>
           <t>☐ Otro acto: ____________</t>
         </is>
@@ -2840,29 +2926,29 @@
       <c r="K21" s="347" t="n"/>
       <c r="L21" s="358" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1" s="127">
-      <c r="A22" s="230" t="inlineStr">
+    <row r="22" ht="29" customHeight="1" s="127">
+      <c r="A22" s="365" t="inlineStr">
         <is>
           <t>☐ Desorden o falta de aseo</t>
         </is>
       </c>
       <c r="B22" s="98" t="n"/>
       <c r="C22" s="97" t="n"/>
-      <c r="D22" s="230" t="inlineStr">
+      <c r="D22" s="365" t="inlineStr">
         <is>
           <t>☐ Herramienta o equipo defectuoso</t>
         </is>
       </c>
       <c r="E22" s="98" t="n"/>
       <c r="F22" s="97" t="n"/>
-      <c r="G22" s="230" t="inlineStr">
+      <c r="G22" s="365" t="inlineStr">
         <is>
           <t>☐ Falta de señalización o demarcación</t>
         </is>
       </c>
       <c r="H22" s="98" t="n"/>
       <c r="I22" s="97" t="n"/>
-      <c r="J22" s="230" t="inlineStr">
+      <c r="J22" s="365" t="inlineStr">
         <is>
           <t>☐ Falta de guardas o protecciones</t>
         </is>
@@ -2870,29 +2956,29 @@
       <c r="K22" s="98" t="n"/>
       <c r="L22" s="97" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1" s="127">
-      <c r="A23" s="72" t="inlineStr">
+    <row r="23" ht="29" customHeight="1" s="127">
+      <c r="A23" s="366" t="inlineStr">
         <is>
           <t>☐ Instalación eléctrica deficiente</t>
         </is>
       </c>
       <c r="B23" s="93" t="n"/>
       <c r="C23" s="89" t="n"/>
-      <c r="D23" s="72" t="inlineStr">
+      <c r="D23" s="366" t="inlineStr">
         <is>
           <t>☐ Andamio, escalera o plataforma en mal estado</t>
         </is>
       </c>
       <c r="E23" s="93" t="n"/>
       <c r="F23" s="89" t="n"/>
-      <c r="G23" s="72" t="inlineStr">
+      <c r="G23" s="366" t="inlineStr">
         <is>
           <t>☐ Iluminación o ventilación insuficiente</t>
         </is>
       </c>
       <c r="H23" s="93" t="n"/>
       <c r="I23" s="89" t="n"/>
-      <c r="J23" s="72" t="inlineStr">
+      <c r="J23" s="366" t="inlineStr">
         <is>
           <t>☐ Piso irregular, húmedo o con huecos</t>
         </is>
@@ -2901,28 +2987,28 @@
       <c r="L23" s="89" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="127">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A24" s="366" t="inlineStr">
         <is>
           <t>☐ Material mal almacenado</t>
         </is>
       </c>
       <c r="B24" s="93" t="n"/>
       <c r="C24" s="89" t="n"/>
-      <c r="D24" s="72" t="inlineStr">
+      <c r="D24" s="366" t="inlineStr">
         <is>
           <t>☐ Fugas o derrames</t>
         </is>
       </c>
       <c r="E24" s="93" t="n"/>
       <c r="F24" s="89" t="n"/>
-      <c r="G24" s="72" t="inlineStr">
+      <c r="G24" s="366" t="inlineStr">
         <is>
           <t>☐ Falta de extintor o de botiquín</t>
         </is>
       </c>
       <c r="H24" s="93" t="n"/>
       <c r="I24" s="89" t="n"/>
-      <c r="J24" s="72" t="inlineStr">
+      <c r="J24" s="366" t="inlineStr">
         <is>
           <t>☐ Otra condición: ____________</t>
         </is>
@@ -2955,16 +3041,16 @@
         </is>
       </c>
       <c r="B26" s="89" t="n"/>
-      <c r="C26" s="100" t="n"/>
-      <c r="D26" s="93" t="n"/>
-      <c r="E26" s="93" t="n"/>
-      <c r="F26" s="93" t="n"/>
-      <c r="G26" s="93" t="n"/>
-      <c r="H26" s="93" t="n"/>
-      <c r="I26" s="93" t="n"/>
-      <c r="J26" s="93" t="n"/>
-      <c r="K26" s="93" t="n"/>
-      <c r="L26" s="89" t="n"/>
+      <c r="C26" s="368" t="n"/>
+      <c r="D26" s="361" t="n"/>
+      <c r="E26" s="361" t="n"/>
+      <c r="F26" s="361" t="n"/>
+      <c r="G26" s="361" t="n"/>
+      <c r="H26" s="361" t="n"/>
+      <c r="I26" s="361" t="n"/>
+      <c r="J26" s="361" t="n"/>
+      <c r="K26" s="361" t="n"/>
+      <c r="L26" s="362" t="n"/>
     </row>
     <row r="27" ht="34.05" customHeight="1" s="127">
       <c r="A27" s="59" t="inlineStr">
@@ -2973,16 +3059,16 @@
         </is>
       </c>
       <c r="B27" s="89" t="n"/>
-      <c r="C27" s="100" t="n"/>
-      <c r="D27" s="93" t="n"/>
-      <c r="E27" s="93" t="n"/>
-      <c r="F27" s="93" t="n"/>
-      <c r="G27" s="93" t="n"/>
-      <c r="H27" s="93" t="n"/>
-      <c r="I27" s="93" t="n"/>
-      <c r="J27" s="93" t="n"/>
-      <c r="K27" s="93" t="n"/>
-      <c r="L27" s="89" t="n"/>
+      <c r="C27" s="368" t="n"/>
+      <c r="D27" s="361" t="n"/>
+      <c r="E27" s="361" t="n"/>
+      <c r="F27" s="361" t="n"/>
+      <c r="G27" s="361" t="n"/>
+      <c r="H27" s="361" t="n"/>
+      <c r="I27" s="361" t="n"/>
+      <c r="J27" s="361" t="n"/>
+      <c r="K27" s="361" t="n"/>
+      <c r="L27" s="362" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="127">
       <c r="A28" s="59" t="inlineStr">
@@ -2991,16 +3077,16 @@
         </is>
       </c>
       <c r="B28" s="89" t="n"/>
-      <c r="C28" s="68" t="n"/>
-      <c r="D28" s="93" t="n"/>
-      <c r="E28" s="93" t="n"/>
-      <c r="F28" s="93" t="n"/>
-      <c r="G28" s="93" t="n"/>
-      <c r="H28" s="93" t="n"/>
-      <c r="I28" s="93" t="n"/>
-      <c r="J28" s="93" t="n"/>
-      <c r="K28" s="93" t="n"/>
-      <c r="L28" s="89" t="n"/>
+      <c r="C28" s="363" t="n"/>
+      <c r="D28" s="361" t="n"/>
+      <c r="E28" s="361" t="n"/>
+      <c r="F28" s="361" t="n"/>
+      <c r="G28" s="361" t="n"/>
+      <c r="H28" s="361" t="n"/>
+      <c r="I28" s="361" t="n"/>
+      <c r="J28" s="361" t="n"/>
+      <c r="K28" s="361" t="n"/>
+      <c r="L28" s="362" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="127">
       <c r="A29" s="59" t="inlineStr">
@@ -3009,24 +3095,24 @@
         </is>
       </c>
       <c r="B29" s="89" t="n"/>
-      <c r="C29" s="69" t="n"/>
-      <c r="D29" s="89" t="n"/>
+      <c r="C29" s="364" t="n"/>
+      <c r="D29" s="362" t="n"/>
       <c r="E29" s="59" t="inlineStr">
         <is>
           <t>Severidad</t>
         </is>
       </c>
       <c r="F29" s="89" t="n"/>
-      <c r="G29" s="69" t="n"/>
-      <c r="H29" s="89" t="n"/>
+      <c r="G29" s="364" t="n"/>
+      <c r="H29" s="362" t="n"/>
       <c r="I29" s="59" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
       <c r="J29" s="89" t="n"/>
-      <c r="K29" s="69" t="n"/>
-      <c r="L29" s="89" t="n"/>
+      <c r="K29" s="364" t="n"/>
+      <c r="L29" s="362" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="127">
       <c r="A30" s="137" t="inlineStr">
@@ -3053,16 +3139,16 @@
         </is>
       </c>
       <c r="B31" s="89" t="n"/>
-      <c r="C31" s="100" t="n"/>
-      <c r="D31" s="93" t="n"/>
-      <c r="E31" s="93" t="n"/>
-      <c r="F31" s="93" t="n"/>
-      <c r="G31" s="93" t="n"/>
-      <c r="H31" s="93" t="n"/>
-      <c r="I31" s="93" t="n"/>
-      <c r="J31" s="93" t="n"/>
-      <c r="K31" s="93" t="n"/>
-      <c r="L31" s="89" t="n"/>
+      <c r="C31" s="368" t="n"/>
+      <c r="D31" s="361" t="n"/>
+      <c r="E31" s="361" t="n"/>
+      <c r="F31" s="361" t="n"/>
+      <c r="G31" s="361" t="n"/>
+      <c r="H31" s="361" t="n"/>
+      <c r="I31" s="361" t="n"/>
+      <c r="J31" s="361" t="n"/>
+      <c r="K31" s="361" t="n"/>
+      <c r="L31" s="362" t="n"/>
     </row>
     <row r="32" ht="34.05" customHeight="1" s="127">
       <c r="A32" s="59" t="inlineStr">
@@ -3071,16 +3157,16 @@
         </is>
       </c>
       <c r="B32" s="89" t="n"/>
-      <c r="C32" s="100" t="n"/>
-      <c r="D32" s="93" t="n"/>
-      <c r="E32" s="93" t="n"/>
-      <c r="F32" s="93" t="n"/>
-      <c r="G32" s="93" t="n"/>
-      <c r="H32" s="93" t="n"/>
-      <c r="I32" s="93" t="n"/>
-      <c r="J32" s="93" t="n"/>
-      <c r="K32" s="93" t="n"/>
-      <c r="L32" s="89" t="n"/>
+      <c r="C32" s="368" t="n"/>
+      <c r="D32" s="361" t="n"/>
+      <c r="E32" s="361" t="n"/>
+      <c r="F32" s="361" t="n"/>
+      <c r="G32" s="361" t="n"/>
+      <c r="H32" s="361" t="n"/>
+      <c r="I32" s="361" t="n"/>
+      <c r="J32" s="361" t="n"/>
+      <c r="K32" s="361" t="n"/>
+      <c r="L32" s="362" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="127">
       <c r="A33" s="59" t="inlineStr">
@@ -3089,20 +3175,20 @@
         </is>
       </c>
       <c r="B33" s="89" t="n"/>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="93" t="n"/>
-      <c r="E33" s="93" t="n"/>
-      <c r="F33" s="93" t="n"/>
-      <c r="G33" s="89" t="n"/>
+      <c r="C33" s="363" t="n"/>
+      <c r="D33" s="361" t="n"/>
+      <c r="E33" s="361" t="n"/>
+      <c r="F33" s="361" t="n"/>
+      <c r="G33" s="362" t="n"/>
       <c r="H33" s="59" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
       </c>
       <c r="I33" s="89" t="n"/>
-      <c r="J33" s="69" t="n"/>
-      <c r="K33" s="93" t="n"/>
-      <c r="L33" s="89" t="n"/>
+      <c r="J33" s="364" t="n"/>
+      <c r="K33" s="361" t="n"/>
+      <c r="L33" s="362" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="127">
       <c r="A34" s="137" t="inlineStr">
@@ -3123,119 +3209,231 @@
       <c r="L34" s="97" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="127">
-      <c r="A35" s="129" t="n"/>
-      <c r="B35" s="104" t="n"/>
-      <c r="C35" s="104" t="n"/>
-      <c r="D35" s="104" t="n"/>
-      <c r="E35" s="104" t="n"/>
-      <c r="F35" s="94" t="n"/>
-      <c r="G35" s="129" t="n"/>
-      <c r="H35" s="104" t="n"/>
-      <c r="I35" s="104" t="n"/>
-      <c r="J35" s="104" t="n"/>
-      <c r="K35" s="104" t="n"/>
-      <c r="L35" s="94" t="n"/>
+      <c r="A35" s="369" t="n"/>
+      <c r="B35" s="370" t="n"/>
+      <c r="C35" s="370" t="n"/>
+      <c r="D35" s="370" t="n"/>
+      <c r="E35" s="370" t="n"/>
+      <c r="F35" s="371" t="n"/>
+      <c r="G35" s="369" t="n"/>
+      <c r="H35" s="370" t="n"/>
+      <c r="I35" s="370" t="n"/>
+      <c r="J35" s="370" t="n"/>
+      <c r="K35" s="370" t="n"/>
+      <c r="L35" s="371" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="127">
-      <c r="A36" s="95" t="n"/>
-      <c r="F36" s="92" t="n"/>
-      <c r="G36" s="95" t="n"/>
-      <c r="L36" s="92" t="n"/>
+      <c r="A36" s="372" t="n"/>
+      <c r="B36" s="373" t="n"/>
+      <c r="C36" s="373" t="n"/>
+      <c r="D36" s="373" t="n"/>
+      <c r="E36" s="373" t="n"/>
+      <c r="F36" s="374" t="n"/>
+      <c r="G36" s="372" t="n"/>
+      <c r="H36" s="373" t="n"/>
+      <c r="I36" s="373" t="n"/>
+      <c r="J36" s="373" t="n"/>
+      <c r="K36" s="373" t="n"/>
+      <c r="L36" s="374" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="127">
-      <c r="A37" s="95" t="n"/>
-      <c r="F37" s="92" t="n"/>
-      <c r="G37" s="95" t="n"/>
-      <c r="L37" s="92" t="n"/>
+      <c r="A37" s="372" t="n"/>
+      <c r="B37" s="373" t="n"/>
+      <c r="C37" s="373" t="n"/>
+      <c r="D37" s="373" t="n"/>
+      <c r="E37" s="373" t="n"/>
+      <c r="F37" s="374" t="n"/>
+      <c r="G37" s="372" t="n"/>
+      <c r="H37" s="373" t="n"/>
+      <c r="I37" s="373" t="n"/>
+      <c r="J37" s="373" t="n"/>
+      <c r="K37" s="373" t="n"/>
+      <c r="L37" s="374" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="127">
-      <c r="A38" s="95" t="n"/>
-      <c r="F38" s="92" t="n"/>
-      <c r="G38" s="95" t="n"/>
-      <c r="L38" s="92" t="n"/>
+      <c r="A38" s="372" t="n"/>
+      <c r="B38" s="373" t="n"/>
+      <c r="C38" s="373" t="n"/>
+      <c r="D38" s="373" t="n"/>
+      <c r="E38" s="373" t="n"/>
+      <c r="F38" s="374" t="n"/>
+      <c r="G38" s="372" t="n"/>
+      <c r="H38" s="373" t="n"/>
+      <c r="I38" s="373" t="n"/>
+      <c r="J38" s="373" t="n"/>
+      <c r="K38" s="373" t="n"/>
+      <c r="L38" s="374" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="127">
-      <c r="A39" s="95" t="n"/>
-      <c r="F39" s="92" t="n"/>
-      <c r="G39" s="95" t="n"/>
-      <c r="L39" s="92" t="n"/>
+      <c r="A39" s="372" t="n"/>
+      <c r="B39" s="373" t="n"/>
+      <c r="C39" s="373" t="n"/>
+      <c r="D39" s="373" t="n"/>
+      <c r="E39" s="373" t="n"/>
+      <c r="F39" s="374" t="n"/>
+      <c r="G39" s="372" t="n"/>
+      <c r="H39" s="373" t="n"/>
+      <c r="I39" s="373" t="n"/>
+      <c r="J39" s="373" t="n"/>
+      <c r="K39" s="373" t="n"/>
+      <c r="L39" s="374" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="127">
-      <c r="A40" s="95" t="n"/>
-      <c r="F40" s="92" t="n"/>
-      <c r="G40" s="95" t="n"/>
-      <c r="L40" s="92" t="n"/>
+      <c r="A40" s="372" t="n"/>
+      <c r="B40" s="373" t="n"/>
+      <c r="C40" s="373" t="n"/>
+      <c r="D40" s="373" t="n"/>
+      <c r="E40" s="373" t="n"/>
+      <c r="F40" s="374" t="n"/>
+      <c r="G40" s="372" t="n"/>
+      <c r="H40" s="373" t="n"/>
+      <c r="I40" s="373" t="n"/>
+      <c r="J40" s="373" t="n"/>
+      <c r="K40" s="373" t="n"/>
+      <c r="L40" s="374" t="n"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="127">
-      <c r="A41" s="95" t="n"/>
-      <c r="F41" s="92" t="n"/>
-      <c r="G41" s="95" t="n"/>
-      <c r="L41" s="92" t="n"/>
+      <c r="A41" s="372" t="n"/>
+      <c r="B41" s="373" t="n"/>
+      <c r="C41" s="373" t="n"/>
+      <c r="D41" s="373" t="n"/>
+      <c r="E41" s="373" t="n"/>
+      <c r="F41" s="374" t="n"/>
+      <c r="G41" s="372" t="n"/>
+      <c r="H41" s="373" t="n"/>
+      <c r="I41" s="373" t="n"/>
+      <c r="J41" s="373" t="n"/>
+      <c r="K41" s="373" t="n"/>
+      <c r="L41" s="374" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="127">
-      <c r="A42" s="95" t="n"/>
-      <c r="F42" s="92" t="n"/>
-      <c r="G42" s="95" t="n"/>
-      <c r="L42" s="92" t="n"/>
+      <c r="A42" s="372" t="n"/>
+      <c r="B42" s="373" t="n"/>
+      <c r="C42" s="373" t="n"/>
+      <c r="D42" s="373" t="n"/>
+      <c r="E42" s="373" t="n"/>
+      <c r="F42" s="374" t="n"/>
+      <c r="G42" s="372" t="n"/>
+      <c r="H42" s="373" t="n"/>
+      <c r="I42" s="373" t="n"/>
+      <c r="J42" s="373" t="n"/>
+      <c r="K42" s="373" t="n"/>
+      <c r="L42" s="374" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="127">
-      <c r="A43" s="95" t="n"/>
-      <c r="F43" s="92" t="n"/>
-      <c r="G43" s="95" t="n"/>
-      <c r="L43" s="92" t="n"/>
+      <c r="A43" s="372" t="n"/>
+      <c r="B43" s="373" t="n"/>
+      <c r="C43" s="373" t="n"/>
+      <c r="D43" s="373" t="n"/>
+      <c r="E43" s="373" t="n"/>
+      <c r="F43" s="374" t="n"/>
+      <c r="G43" s="372" t="n"/>
+      <c r="H43" s="373" t="n"/>
+      <c r="I43" s="373" t="n"/>
+      <c r="J43" s="373" t="n"/>
+      <c r="K43" s="373" t="n"/>
+      <c r="L43" s="374" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="127">
-      <c r="A44" s="95" t="n"/>
-      <c r="F44" s="92" t="n"/>
-      <c r="G44" s="95" t="n"/>
-      <c r="L44" s="92" t="n"/>
+      <c r="A44" s="372" t="n"/>
+      <c r="B44" s="373" t="n"/>
+      <c r="C44" s="373" t="n"/>
+      <c r="D44" s="373" t="n"/>
+      <c r="E44" s="373" t="n"/>
+      <c r="F44" s="374" t="n"/>
+      <c r="G44" s="372" t="n"/>
+      <c r="H44" s="373" t="n"/>
+      <c r="I44" s="373" t="n"/>
+      <c r="J44" s="373" t="n"/>
+      <c r="K44" s="373" t="n"/>
+      <c r="L44" s="374" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="127">
-      <c r="A45" s="95" t="n"/>
-      <c r="F45" s="92" t="n"/>
-      <c r="G45" s="95" t="n"/>
-      <c r="L45" s="92" t="n"/>
+      <c r="A45" s="372" t="n"/>
+      <c r="B45" s="373" t="n"/>
+      <c r="C45" s="373" t="n"/>
+      <c r="D45" s="373" t="n"/>
+      <c r="E45" s="373" t="n"/>
+      <c r="F45" s="374" t="n"/>
+      <c r="G45" s="372" t="n"/>
+      <c r="H45" s="373" t="n"/>
+      <c r="I45" s="373" t="n"/>
+      <c r="J45" s="373" t="n"/>
+      <c r="K45" s="373" t="n"/>
+      <c r="L45" s="374" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="127">
-      <c r="A46" s="95" t="n"/>
-      <c r="F46" s="92" t="n"/>
-      <c r="G46" s="95" t="n"/>
-      <c r="L46" s="92" t="n"/>
+      <c r="A46" s="372" t="n"/>
+      <c r="B46" s="373" t="n"/>
+      <c r="C46" s="373" t="n"/>
+      <c r="D46" s="373" t="n"/>
+      <c r="E46" s="373" t="n"/>
+      <c r="F46" s="374" t="n"/>
+      <c r="G46" s="372" t="n"/>
+      <c r="H46" s="373" t="n"/>
+      <c r="I46" s="373" t="n"/>
+      <c r="J46" s="373" t="n"/>
+      <c r="K46" s="373" t="n"/>
+      <c r="L46" s="374" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="127">
-      <c r="A47" s="95" t="n"/>
-      <c r="F47" s="92" t="n"/>
-      <c r="G47" s="95" t="n"/>
-      <c r="L47" s="92" t="n"/>
+      <c r="A47" s="372" t="n"/>
+      <c r="B47" s="373" t="n"/>
+      <c r="C47" s="373" t="n"/>
+      <c r="D47" s="373" t="n"/>
+      <c r="E47" s="373" t="n"/>
+      <c r="F47" s="374" t="n"/>
+      <c r="G47" s="372" t="n"/>
+      <c r="H47" s="373" t="n"/>
+      <c r="I47" s="373" t="n"/>
+      <c r="J47" s="373" t="n"/>
+      <c r="K47" s="373" t="n"/>
+      <c r="L47" s="374" t="n"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="127">
-      <c r="A48" s="95" t="n"/>
-      <c r="F48" s="92" t="n"/>
-      <c r="G48" s="95" t="n"/>
-      <c r="L48" s="92" t="n"/>
+      <c r="A48" s="372" t="n"/>
+      <c r="B48" s="373" t="n"/>
+      <c r="C48" s="373" t="n"/>
+      <c r="D48" s="373" t="n"/>
+      <c r="E48" s="373" t="n"/>
+      <c r="F48" s="374" t="n"/>
+      <c r="G48" s="372" t="n"/>
+      <c r="H48" s="373" t="n"/>
+      <c r="I48" s="373" t="n"/>
+      <c r="J48" s="373" t="n"/>
+      <c r="K48" s="373" t="n"/>
+      <c r="L48" s="374" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="127">
-      <c r="A49" s="95" t="n"/>
-      <c r="F49" s="92" t="n"/>
-      <c r="G49" s="95" t="n"/>
-      <c r="L49" s="92" t="n"/>
+      <c r="A49" s="372" t="n"/>
+      <c r="B49" s="373" t="n"/>
+      <c r="C49" s="373" t="n"/>
+      <c r="D49" s="373" t="n"/>
+      <c r="E49" s="373" t="n"/>
+      <c r="F49" s="374" t="n"/>
+      <c r="G49" s="372" t="n"/>
+      <c r="H49" s="373" t="n"/>
+      <c r="I49" s="373" t="n"/>
+      <c r="J49" s="373" t="n"/>
+      <c r="K49" s="373" t="n"/>
+      <c r="L49" s="374" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="127">
-      <c r="A50" s="96" t="n"/>
-      <c r="B50" s="98" t="n"/>
-      <c r="C50" s="98" t="n"/>
-      <c r="D50" s="98" t="n"/>
-      <c r="E50" s="98" t="n"/>
-      <c r="F50" s="97" t="n"/>
-      <c r="G50" s="96" t="n"/>
-      <c r="H50" s="98" t="n"/>
-      <c r="I50" s="98" t="n"/>
-      <c r="J50" s="98" t="n"/>
-      <c r="K50" s="98" t="n"/>
-      <c r="L50" s="97" t="n"/>
+      <c r="A50" s="375" t="n"/>
+      <c r="B50" s="376" t="n"/>
+      <c r="C50" s="376" t="n"/>
+      <c r="D50" s="376" t="n"/>
+      <c r="E50" s="376" t="n"/>
+      <c r="F50" s="377" t="n"/>
+      <c r="G50" s="375" t="n"/>
+      <c r="H50" s="376" t="n"/>
+      <c r="I50" s="376" t="n"/>
+      <c r="J50" s="376" t="n"/>
+      <c r="K50" s="376" t="n"/>
+      <c r="L50" s="377" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="127">
-      <c r="A51" s="130" t="inlineStr">
+      <c r="A51" s="378" t="inlineStr">
         <is>
           <t>ANTES — el acto o la condición observada</t>
         </is>
@@ -3245,7 +3443,7 @@
       <c r="D51" s="93" t="n"/>
       <c r="E51" s="93" t="n"/>
       <c r="F51" s="89" t="n"/>
-      <c r="G51" s="130" t="inlineStr">
+      <c r="G51" s="378" t="inlineStr">
         <is>
           <t>DESPUÉS — ya corregido (cuando aplique)</t>
         </is>
@@ -3281,24 +3479,24 @@
         </is>
       </c>
       <c r="B53" s="89" t="n"/>
-      <c r="C53" s="69" t="n"/>
-      <c r="D53" s="89" t="n"/>
+      <c r="C53" s="364" t="n"/>
+      <c r="D53" s="362" t="n"/>
       <c r="E53" s="59" t="inlineStr">
         <is>
           <t>Fecha de cierre</t>
         </is>
       </c>
       <c r="F53" s="89" t="n"/>
-      <c r="G53" s="69" t="n"/>
-      <c r="H53" s="89" t="n"/>
+      <c r="G53" s="364" t="n"/>
+      <c r="H53" s="362" t="n"/>
       <c r="I53" s="59" t="inlineStr">
         <is>
           <t>Verificó el cierre</t>
         </is>
       </c>
       <c r="J53" s="89" t="n"/>
-      <c r="K53" s="68" t="n"/>
-      <c r="L53" s="89" t="n"/>
+      <c r="K53" s="363" t="n"/>
+      <c r="L53" s="362" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1" s="127">
       <c r="A54" s="59" t="inlineStr">
@@ -3307,16 +3505,16 @@
         </is>
       </c>
       <c r="B54" s="89" t="n"/>
-      <c r="C54" s="100" t="n"/>
-      <c r="D54" s="93" t="n"/>
-      <c r="E54" s="93" t="n"/>
-      <c r="F54" s="93" t="n"/>
-      <c r="G54" s="93" t="n"/>
-      <c r="H54" s="93" t="n"/>
-      <c r="I54" s="93" t="n"/>
-      <c r="J54" s="93" t="n"/>
-      <c r="K54" s="93" t="n"/>
-      <c r="L54" s="89" t="n"/>
+      <c r="C54" s="368" t="n"/>
+      <c r="D54" s="361" t="n"/>
+      <c r="E54" s="361" t="n"/>
+      <c r="F54" s="361" t="n"/>
+      <c r="G54" s="361" t="n"/>
+      <c r="H54" s="361" t="n"/>
+      <c r="I54" s="361" t="n"/>
+      <c r="J54" s="361" t="n"/>
+      <c r="K54" s="361" t="n"/>
+      <c r="L54" s="362" t="n"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="127">
       <c r="A55" s="227" t="inlineStr">
@@ -3359,24 +3557,24 @@
         </is>
       </c>
       <c r="B57" s="97" t="n"/>
-      <c r="C57" s="301" t="n"/>
-      <c r="D57" s="97" t="n"/>
+      <c r="C57" s="379" t="n"/>
+      <c r="D57" s="377" t="n"/>
       <c r="E57" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F57" s="97" t="n"/>
-      <c r="G57" s="301" t="n"/>
-      <c r="H57" s="97" t="n"/>
+      <c r="G57" s="379" t="n"/>
+      <c r="H57" s="377" t="n"/>
       <c r="I57" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J57" s="97" t="n"/>
-      <c r="K57" s="301" t="n"/>
-      <c r="L57" s="97" t="n"/>
+      <c r="K57" s="379" t="n"/>
+      <c r="L57" s="377" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1" s="127">
       <c r="A58" s="70" t="inlineStr">
@@ -3385,24 +3583,24 @@
         </is>
       </c>
       <c r="B58" s="89" t="n"/>
-      <c r="C58" s="68" t="n"/>
-      <c r="D58" s="89" t="n"/>
+      <c r="C58" s="363" t="n"/>
+      <c r="D58" s="362" t="n"/>
       <c r="E58" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F58" s="89" t="n"/>
-      <c r="G58" s="68" t="n"/>
-      <c r="H58" s="89" t="n"/>
+      <c r="G58" s="363" t="n"/>
+      <c r="H58" s="362" t="n"/>
       <c r="I58" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J58" s="89" t="n"/>
-      <c r="K58" s="68" t="n"/>
-      <c r="L58" s="89" t="n"/>
+      <c r="K58" s="363" t="n"/>
+      <c r="L58" s="362" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1" s="127">
       <c r="A59" s="70" t="inlineStr">
@@ -3411,24 +3609,24 @@
         </is>
       </c>
       <c r="B59" s="89" t="n"/>
-      <c r="C59" s="68" t="n"/>
-      <c r="D59" s="89" t="n"/>
+      <c r="C59" s="363" t="n"/>
+      <c r="D59" s="362" t="n"/>
       <c r="E59" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F59" s="89" t="n"/>
-      <c r="G59" s="68" t="n"/>
-      <c r="H59" s="89" t="n"/>
+      <c r="G59" s="363" t="n"/>
+      <c r="H59" s="362" t="n"/>
       <c r="I59" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J59" s="89" t="n"/>
-      <c r="K59" s="68" t="n"/>
-      <c r="L59" s="89" t="n"/>
+      <c r="K59" s="363" t="n"/>
+      <c r="L59" s="362" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="25" t="inlineStr">
@@ -3442,6 +3640,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="112">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A21:L21"/>
